--- a/workspaces/cobranza/estadisticas/ESTADISTICA_2026_CON_DROPDOWN.xlsx
+++ b/workspaces/cobranza/estadisticas/ESTADISTICA_2026_CON_DROPDOWN.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="$#,##0"/>
     <numFmt numFmtId="168" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="69">
+  <fonts count="91">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -427,8 +427,109 @@
       <color rgb="00808080"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002E5FA3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="002E5FA3"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002E5FA3"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="31">
     <fill>
       <patternFill/>
     </fill>
@@ -533,6 +634,60 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C9A227"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+        <bgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E5FA3"/>
+        <bgColor rgb="002E5FA3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+        <bgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00375623"/>
+        <bgColor rgb="00375623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DAE8F7"/>
+        <bgColor rgb="00DAE8F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+        <bgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -1204,7 +1359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="277">
+  <cellXfs count="332">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1975,6 +2130,171 @@
     </xf>
     <xf numFmtId="165" fontId="2" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="25" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="23" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="72" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="75" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="9" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="82" fillId="15" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="82" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="82" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="83" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="83" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="83" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="23" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="26" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="23" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="23" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="26" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="69" fillId="23" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="69" fillId="26" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="22" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="23" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="24" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="85" fillId="24" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="86" fillId="24" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="24" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="27" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="85" fillId="27" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="86" fillId="27" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="27" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="28" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="85" fillId="28" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="86" fillId="28" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="28" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="29" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="85" fillId="29" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="86" fillId="29" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="29" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="30" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="89" fillId="30" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="90" fillId="30" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="30" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2360,22 +2680,22 @@
     <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="86" t="inlineStr">
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="289" t="inlineStr">
         <is>
           <t>PROTEG-RT MUTUALIDAD</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="87" t="inlineStr">
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="290" t="inlineStr">
         <is>
           <t>DASHBOARD — REPORTE DE COBRANZA JUNTA MENSUAL</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="204" t="inlineStr">
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="291" t="inlineStr">
         <is>
           <t>AÑO 2026</t>
         </is>
@@ -2397,13 +2717,13 @@
       <c r="M4" s="89" t="n"/>
       <c r="N4" s="89" t="n"/>
     </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="90" t="inlineStr">
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="292" t="inlineStr">
         <is>
           <t>MES:</t>
         </is>
       </c>
-      <c r="C5" s="91" t="inlineStr">
+      <c r="C5" s="293" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
@@ -2414,15 +2734,15 @@
           <t>AÑO:</t>
         </is>
       </c>
-      <c r="G5" s="91" t="inlineStr">
+      <c r="G5" s="293" t="inlineStr">
         <is>
           <t>← Cambia el mes aquí</t>
         </is>
       </c>
       <c r="H5" s="162" t="n"/>
     </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="217" t="inlineStr">
+    <row r="7" ht="55" customHeight="1">
+      <c r="A7" s="294" t="inlineStr">
         <is>
           <t>COBRANZA
 TOTAL GENERAL</t>
@@ -2430,7 +2750,7 @@
       </c>
       <c r="B7" s="45" t="n"/>
       <c r="C7" s="46" t="n"/>
-      <c r="D7" s="218" t="inlineStr">
+      <c r="D7" s="295" t="inlineStr">
         <is>
           <t>COBRANZA
 RECUPERADA</t>
@@ -2438,7 +2758,7 @@
       </c>
       <c r="E7" s="45" t="n"/>
       <c r="F7" s="46" t="n"/>
-      <c r="G7" s="219" t="inlineStr">
+      <c r="G7" s="296" t="inlineStr">
         <is>
           <t>COBRANZA
 EFECTIVA</t>
@@ -2456,20 +2776,20 @@
       <c r="M7" s="38" t="n"/>
       <c r="N7" s="38" t="n"/>
     </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="221">
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="297">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871)))</f>
         <v/>
       </c>
       <c r="B8" s="163" t="n"/>
       <c r="C8" s="164" t="n"/>
-      <c r="D8" s="222">
+      <c r="D8" s="298">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),48,122,196,270,344,418,492,566,640,714,788,862)))</f>
         <v/>
       </c>
       <c r="E8" s="171" t="n"/>
       <c r="F8" s="172" t="n"/>
-      <c r="G8" s="223">
+      <c r="G8" s="299">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),39,113,187,261,335,409,483,557,631,705,779,853)))</f>
         <v/>
       </c>
@@ -2484,20 +2804,20 @@
       <c r="M8" s="38" t="n"/>
       <c r="N8" s="38" t="n"/>
     </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="264">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="300">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),11,85,159,233,307,381,455,529,603,677,751,825)))/INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871))</f>
         <v/>
       </c>
       <c r="B9" s="45" t="n"/>
       <c r="C9" s="46" t="n"/>
-      <c r="D9" s="265">
+      <c r="D9" s="301">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),48,122,196,270,344,418,492,566,640,714,788,862)))/INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871))</f>
         <v/>
       </c>
       <c r="E9" s="45" t="n"/>
       <c r="F9" s="46" t="n"/>
-      <c r="G9" s="266">
+      <c r="G9" s="302">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),39,113,187,261,335,409,483,557,631,705,779,853)))/INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871))</f>
         <v/>
       </c>
@@ -2528,8 +2848,8 @@
       <c r="M10" s="38" t="n"/>
       <c r="N10" s="38" t="n"/>
     </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="217" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="303" t="inlineStr">
         <is>
           <t>COBRANZA
 CORRIENTE</t>
@@ -2537,7 +2857,7 @@
       </c>
       <c r="B11" s="45" t="n"/>
       <c r="C11" s="46" t="n"/>
-      <c r="D11" s="229" t="inlineStr">
+      <c r="D11" s="303" t="inlineStr">
         <is>
           <t>COBRANZA
 VENCIDA</t>
@@ -2545,7 +2865,7 @@
       </c>
       <c r="E11" s="45" t="n"/>
       <c r="F11" s="46" t="n"/>
-      <c r="G11" s="230" t="inlineStr">
+      <c r="G11" s="304" t="inlineStr">
         <is>
           <t>COBRANZA
 ANTICIPADA</t>
@@ -2564,20 +2884,20 @@
       <c r="M11" s="38" t="n"/>
       <c r="N11" s="38" t="n"/>
     </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="221">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="305">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),11,85,159,233,307,381,455,529,603,677,751,825)))</f>
         <v/>
       </c>
       <c r="B12" s="163" t="n"/>
       <c r="C12" s="164" t="n"/>
-      <c r="D12" s="232">
+      <c r="D12" s="306">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),35,109,183,257,331,405,479,553,627,701,775,849)))</f>
         <v/>
       </c>
       <c r="E12" s="167" t="n"/>
       <c r="F12" s="168" t="n"/>
-      <c r="G12" s="233">
+      <c r="G12" s="307">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),66,140,214,288,362,436,510,584,658,732,806,880)))</f>
         <v/>
       </c>
@@ -2592,21 +2912,21 @@
       <c r="M12" s="38" t="n"/>
       <c r="N12" s="38" t="n"/>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="225" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="303" t="inlineStr">
         <is>
           <t>Total del mes</t>
         </is>
       </c>
       <c r="B13" s="45" t="n"/>
       <c r="C13" s="46" t="n"/>
-      <c r="D13" s="268">
+      <c r="D13" s="308">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),35,109,183,257,331,405,479,553,627,701,775,849)))/INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871))</f>
         <v/>
       </c>
       <c r="E13" s="45" t="n"/>
       <c r="F13" s="46" t="n"/>
-      <c r="G13" s="269">
+      <c r="G13" s="309">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),66,140,214,288,362,436,510,584,658,732,806,880)))/INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871))</f>
         <v/>
       </c>
@@ -2621,14 +2941,14 @@
       <c r="M13" s="38" t="n"/>
       <c r="N13" s="38" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="38" t="n"/>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="303" t="n"/>
       <c r="B14" s="38" t="n"/>
       <c r="C14" s="38" t="n"/>
-      <c r="D14" s="38" t="n"/>
+      <c r="D14" s="303" t="n"/>
       <c r="E14" s="38" t="n"/>
       <c r="F14" s="38" t="n"/>
-      <c r="G14" s="38" t="n"/>
+      <c r="G14" s="304" t="n"/>
       <c r="H14" s="38" t="n"/>
       <c r="I14" s="38" t="n"/>
       <c r="J14" s="38" t="n"/>
@@ -2654,7 +2974,7 @@
       <c r="N15" s="238" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="113" t="inlineStr">
+      <c r="A16" s="310" t="inlineStr">
         <is>
           <t>CONCENTRADO GENERAL — DISTRIBUCIÓN DEL MES</t>
         </is>
@@ -2674,24 +2994,24 @@
       <c r="N16" s="115" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="116" t="inlineStr">
+      <c r="A17" s="311" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
         </is>
       </c>
-      <c r="B17" s="116" t="inlineStr">
+      <c r="B17" s="311" t="inlineStr">
         <is>
           <t>TOTAL ($)</t>
         </is>
       </c>
       <c r="C17" s="38" t="n"/>
-      <c r="D17" s="116" t="inlineStr">
+      <c r="D17" s="311" t="inlineStr">
         <is>
           <t>% PARTICIP.</t>
         </is>
       </c>
       <c r="E17" s="38" t="n"/>
-      <c r="F17" s="116" t="inlineStr">
+      <c r="F17" s="311" t="inlineStr">
         <is>
           <t>ESTATUS</t>
         </is>
@@ -2706,22 +3026,22 @@
       <c r="N17" s="38" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="176" t="inlineStr">
+      <c r="A18" s="312" t="inlineStr">
         <is>
           <t>COBRANZA TOTAL GENERAL</t>
         </is>
       </c>
-      <c r="B18" s="177">
+      <c r="B18" s="313">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871)))</f>
         <v/>
       </c>
       <c r="C18" s="38" t="n"/>
-      <c r="D18" s="271">
+      <c r="D18" s="314">
         <f>B18/B23</f>
         <v/>
       </c>
       <c r="E18" s="38" t="n"/>
-      <c r="F18" s="179" t="inlineStr">
+      <c r="F18" s="315" t="inlineStr">
         <is>
           <t>Base del periodo</t>
         </is>
@@ -2736,22 +3056,22 @@
       <c r="N18" s="38" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="180" t="inlineStr">
+      <c r="A19" s="316" t="inlineStr">
         <is>
           <t>COBRANZA RECUPERADA</t>
         </is>
       </c>
-      <c r="B19" s="181">
+      <c r="B19" s="317">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),48,122,196,270,344,418,492,566,640,714,788,862)))</f>
         <v/>
       </c>
       <c r="C19" s="38" t="n"/>
-      <c r="D19" s="272">
+      <c r="D19" s="318">
         <f>B19/B23</f>
         <v/>
       </c>
       <c r="E19" s="38" t="n"/>
-      <c r="F19" s="183" t="inlineStr">
+      <c r="F19" s="319" t="inlineStr">
         <is>
           <t>Acumulado del mes</t>
         </is>
@@ -2766,22 +3086,22 @@
       <c r="N19" s="38" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="184" t="inlineStr">
+      <c r="A20" s="320" t="inlineStr">
         <is>
           <t>COBRANZA EFECTIVA</t>
         </is>
       </c>
-      <c r="B20" s="185">
+      <c r="B20" s="321">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),39,113,187,261,335,409,483,557,631,705,779,853)))</f>
         <v/>
       </c>
       <c r="C20" s="38" t="n"/>
-      <c r="D20" s="273">
+      <c r="D20" s="322">
         <f>B20/B23</f>
         <v/>
       </c>
       <c r="E20" s="38" t="n"/>
-      <c r="F20" s="187" t="inlineStr">
+      <c r="F20" s="323" t="inlineStr">
         <is>
           <t>Cobrado en el mes</t>
         </is>
@@ -2796,22 +3116,22 @@
       <c r="N20" s="38" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="188" t="inlineStr">
+      <c r="A21" s="324" t="inlineStr">
         <is>
           <t>CANCELACIONES</t>
         </is>
       </c>
-      <c r="B21" s="189">
+      <c r="B21" s="325">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),30,104,178,252,326,400,474,548,622,696,770,844)))</f>
         <v/>
       </c>
       <c r="C21" s="38" t="n"/>
-      <c r="D21" s="274">
+      <c r="D21" s="326">
         <f>B21/B23</f>
         <v/>
       </c>
       <c r="E21" s="38" t="n"/>
-      <c r="F21" s="191" t="inlineStr">
+      <c r="F21" s="327" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -2826,22 +3146,22 @@
       <c r="N21" s="38" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="192" t="inlineStr">
+      <c r="A22" s="324" t="inlineStr">
         <is>
           <t>COBRANZA VENCIDA</t>
         </is>
       </c>
-      <c r="B22" s="193">
+      <c r="B22" s="325">
         <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),35,109,183,257,331,405,479,553,627,701,775,849)))</f>
         <v/>
       </c>
       <c r="C22" s="38" t="n"/>
-      <c r="D22" s="275">
+      <c r="D22" s="326">
         <f>B22/B23</f>
         <v/>
       </c>
       <c r="E22" s="38" t="n"/>
-      <c r="F22" s="195" t="inlineStr">
+      <c r="F22" s="327" t="inlineStr">
         <is>
           <t>En riesgo</t>
         </is>
@@ -2855,23 +3175,23 @@
       <c r="M22" s="38" t="n"/>
       <c r="N22" s="38" t="n"/>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="196" t="inlineStr">
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="328" t="inlineStr">
         <is>
           <t>TOTAL ACUMULADO</t>
         </is>
       </c>
-      <c r="B23" s="197">
+      <c r="B23" s="329">
         <f>B18+B19+B20+B21+B22</f>
         <v/>
       </c>
       <c r="C23" s="130" t="n"/>
-      <c r="D23" s="276">
+      <c r="D23" s="330">
         <f>B23/B23</f>
         <v/>
       </c>
       <c r="E23" s="130" t="n"/>
-      <c r="F23" s="199" t="inlineStr">
+      <c r="F23" s="331" t="inlineStr">
         <is>
           <t>Suma de todos los conceptos</t>
         </is>
@@ -3883,13 +4203,13 @@
   <dimension ref="A1:P914"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -3899,36 +4219,36 @@
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PROTEG-RT MUTUALIDAD</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="277" t="inlineStr">
         <is>
           <t>REPORTE DE COBRANZA — JUNTA MENSUAL</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>AÑO 2026</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="8" customHeight="1"/>
-    <row r="5" ht="22" customHeight="1">
+    <row r="4" ht="18" customHeight="1"/>
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>ENERO 2026</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="34" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
@@ -4000,14 +4320,14 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Mes</t>
@@ -4027,7 +4347,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Fecha de corte</t>
@@ -4041,7 +4361,7 @@
       </c>
       <c r="F9" s="10" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="36" t="inlineStr">
         <is>
           <t>COBRANZA CORRIENTE</t>
@@ -4061,7 +4381,7 @@
       <c r="M10" s="38" t="n"/>
       <c r="N10" s="38" t="n"/>
     </row>
-    <row r="11" ht="6" customHeight="1">
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" s="40" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4083,7 +4403,7 @@
       <c r="M11" s="38" t="n"/>
       <c r="N11" s="38" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="42" t="n"/>
       <c r="B12" s="43" t="inlineStr">
         <is>
@@ -4103,7 +4423,7 @@
       <c r="M12" s="38" t="n"/>
       <c r="N12" s="38" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1">
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="240" t="n"/>
       <c r="B13" s="45" t="n"/>
       <c r="C13" s="45" t="n"/>
@@ -4229,7 +4549,7 @@
       <c r="O19" s="70" t="n"/>
       <c r="P19" s="70" t="n"/>
     </row>
-    <row r="20" ht="20" customHeight="1">
+    <row r="20" ht="18" customHeight="1">
       <c r="A20" s="255" t="n"/>
       <c r="B20" s="256" t="n"/>
       <c r="C20" s="257" t="n"/>
@@ -4247,7 +4567,7 @@
       <c r="O20" s="70" t="n"/>
       <c r="P20" s="70" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="18" customHeight="1">
       <c r="A21" s="84" t="inlineStr">
         <is>
           <t>Top 5</t>
@@ -4449,7 +4769,7 @@
       <c r="M28" s="53" t="n"/>
       <c r="N28" s="53" t="n"/>
     </row>
-    <row r="29" ht="6" customHeight="1">
+    <row r="29" ht="18" customHeight="1">
       <c r="A29" s="38" t="n"/>
       <c r="B29" s="38" t="n"/>
       <c r="C29" s="38" t="n"/>
@@ -4465,7 +4785,7 @@
       <c r="M29" s="38" t="n"/>
       <c r="N29" s="38" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="18" customHeight="1">
       <c r="A30" s="42" t="n"/>
       <c r="B30" s="45" t="n"/>
       <c r="C30" s="45" t="n"/>
@@ -4481,7 +4801,7 @@
       <c r="M30" s="45" t="n"/>
       <c r="N30" s="46" t="n"/>
     </row>
-    <row r="31" ht="20" customHeight="1">
+    <row r="31" ht="18" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4660,8 +4980,8 @@
         <v>0.7016424016363855</v>
       </c>
     </row>
-    <row r="38" ht="6" customHeight="1"/>
-    <row r="39">
+    <row r="38" ht="18" customHeight="1"/>
+    <row r="39" ht="18" customHeight="1">
       <c r="A39" s="35" t="inlineStr">
         <is>
           <t>COBRANZA EFECTIVA</t>
@@ -4681,7 +5001,7 @@
       <c r="M39" s="28" t="n"/>
       <c r="N39" s="28" t="n"/>
     </row>
-    <row r="40" ht="20" customHeight="1">
+    <row r="40" ht="18" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4860,8 +5180,8 @@
         <v>0.5959642561889325</v>
       </c>
     </row>
-    <row r="47" ht="6" customHeight="1"/>
-    <row r="48">
+    <row r="47" ht="18" customHeight="1"/>
+    <row r="48" ht="18" customHeight="1">
       <c r="A48" s="35" t="inlineStr">
         <is>
           <t>COBRANZA RECUPERADA</t>
@@ -4881,7 +5201,7 @@
       <c r="M48" s="28" t="n"/>
       <c r="N48" s="28" t="n"/>
     </row>
-    <row r="49" ht="20" customHeight="1">
+    <row r="49" ht="18" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5060,8 +5380,8 @@
         <v>0.7300502268449041</v>
       </c>
     </row>
-    <row r="56" ht="6" customHeight="1"/>
-    <row r="57">
+    <row r="56" ht="18" customHeight="1"/>
+    <row r="57" ht="18" customHeight="1">
       <c r="A57" s="35" t="inlineStr">
         <is>
           <t>COBRANZA TOTAL GENERAL</t>
@@ -5081,7 +5401,7 @@
       <c r="M57" s="28" t="n"/>
       <c r="N57" s="28" t="n"/>
     </row>
-    <row r="58" ht="20" customHeight="1">
+    <row r="58" ht="18" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5260,8 +5580,8 @@
         <v>0.5878838088260767</v>
       </c>
     </row>
-    <row r="65" ht="6" customHeight="1"/>
-    <row r="66">
+    <row r="65" ht="18" customHeight="1"/>
+    <row r="66" ht="18" customHeight="1">
       <c r="A66" s="35" t="inlineStr">
         <is>
           <t>COBRANZA ADELANTADA F.</t>
@@ -5281,7 +5601,7 @@
       <c r="M66" s="28" t="n"/>
       <c r="N66" s="28" t="n"/>
     </row>
-    <row r="67" ht="20" customHeight="1">
+    <row r="67" ht="18" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5450,8 +5770,8 @@
       <c r="M73" s="15" t="n"/>
       <c r="N73" s="15" t="n"/>
     </row>
-    <row r="74" ht="6" customHeight="1"/>
-    <row r="75">
+    <row r="74" ht="18" customHeight="1"/>
+    <row r="75" ht="18" customHeight="1">
       <c r="A75" s="82" t="inlineStr">
         <is>
           <t>PROYECCION ENERO  FEBRERO</t>
@@ -5471,7 +5791,7 @@
       <c r="M75" s="28" t="n"/>
       <c r="N75" s="28" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="18" customHeight="1">
       <c r="A76" s="19" t="inlineStr">
         <is>
           <t>Proyeccion FEBRERO</t>
@@ -5481,15 +5801,16 @@
         <v>1158184</v>
       </c>
     </row>
-    <row r="78" ht="14" customHeight="1"/>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
+    <row r="77" ht="18" customHeight="1"/>
+    <row r="78" ht="18" customHeight="1"/>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="277" t="inlineStr">
         <is>
           <t>FEBRERO 2026</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="28" customHeight="1">
+    <row r="80" ht="18" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
@@ -5556,7 +5877,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="18" customHeight="1">
       <c r="A81" s="35" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
@@ -5576,7 +5897,7 @@
       <c r="M81" s="28" t="n"/>
       <c r="N81" s="28" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="18" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
         <is>
           <t>Mes</t>
@@ -5598,7 +5919,7 @@
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="18" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
           <t>Fecha de corte</t>
@@ -5612,7 +5933,7 @@
       </c>
       <c r="F83" s="10" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="18" customHeight="1">
       <c r="A84" s="8" t="inlineStr">
         <is>
           <t>Reportado por</t>
@@ -5626,8 +5947,8 @@
       </c>
       <c r="F84" s="10" t="n"/>
     </row>
-    <row r="85" ht="6" customHeight="1"/>
-    <row r="86">
+    <row r="85" ht="18" customHeight="1"/>
+    <row r="86" ht="18" customHeight="1">
       <c r="A86" s="35" t="inlineStr">
         <is>
           <t>COBRANZA CORRIENTE</t>
@@ -5647,7 +5968,7 @@
       <c r="M86" s="28" t="n"/>
       <c r="N86" s="28" t="n"/>
     </row>
-    <row r="87" ht="20" customHeight="1">
+    <row r="87" ht="18" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5774,8 +6095,8 @@
       <c r="M93" s="15" t="n"/>
       <c r="N93" s="15" t="n"/>
     </row>
-    <row r="94" ht="6" customHeight="1"/>
-    <row r="95">
+    <row r="94" ht="18" customHeight="1"/>
+    <row r="95" ht="18" customHeight="1">
       <c r="A95" s="35" t="inlineStr">
         <is>
           <t>CANCELACIONES</t>
@@ -5795,7 +6116,7 @@
       <c r="M95" s="28" t="n"/>
       <c r="N95" s="28" t="n"/>
     </row>
-    <row r="96" ht="20" customHeight="1">
+    <row r="96" ht="18" customHeight="1">
       <c r="A96" s="16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5922,8 +6243,8 @@
       <c r="M102" s="15" t="n"/>
       <c r="N102" s="15" t="n"/>
     </row>
-    <row r="103" ht="6" customHeight="1"/>
-    <row r="104">
+    <row r="103" ht="18" customHeight="1"/>
+    <row r="104" ht="18" customHeight="1">
       <c r="A104" s="35" t="inlineStr">
         <is>
           <t>COBRANZA VENCIDA</t>
@@ -5943,7 +6264,7 @@
       <c r="M104" s="28" t="n"/>
       <c r="N104" s="28" t="n"/>
     </row>
-    <row r="105" ht="20" customHeight="1">
+    <row r="105" ht="18" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6122,8 +6443,8 @@
         <v>0.8142</v>
       </c>
     </row>
-    <row r="112" ht="6" customHeight="1"/>
-    <row r="113">
+    <row r="112" ht="18" customHeight="1"/>
+    <row r="113" ht="18" customHeight="1">
       <c r="A113" s="35" t="inlineStr">
         <is>
           <t>COBRANZA EFECTIVA</t>
@@ -6143,7 +6464,7 @@
       <c r="M113" s="28" t="n"/>
       <c r="N113" s="28" t="n"/>
     </row>
-    <row r="114" ht="20" customHeight="1">
+    <row r="114" ht="18" customHeight="1">
       <c r="A114" s="16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6270,8 +6591,8 @@
       <c r="M120" s="15" t="n"/>
       <c r="N120" s="15" t="n"/>
     </row>
-    <row r="121" ht="6" customHeight="1"/>
-    <row r="122">
+    <row r="121" ht="18" customHeight="1"/>
+    <row r="122" ht="18" customHeight="1">
       <c r="A122" s="35" t="inlineStr">
         <is>
           <t>COBRANZA RECUPERADA</t>
@@ -6291,7 +6612,7 @@
       <c r="M122" s="28" t="n"/>
       <c r="N122" s="28" t="n"/>
     </row>
-    <row r="123" ht="20" customHeight="1">
+    <row r="123" ht="18" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6418,8 +6739,8 @@
       <c r="M129" s="15" t="n"/>
       <c r="N129" s="15" t="n"/>
     </row>
-    <row r="130" ht="6" customHeight="1"/>
-    <row r="131">
+    <row r="130" ht="18" customHeight="1"/>
+    <row r="131" ht="18" customHeight="1">
       <c r="A131" s="35" t="inlineStr">
         <is>
           <t>COBRANZA TOTAL GENERAL</t>
@@ -6439,7 +6760,7 @@
       <c r="M131" s="28" t="n"/>
       <c r="N131" s="28" t="n"/>
     </row>
-    <row r="132" ht="20" customHeight="1">
+    <row r="132" ht="18" customHeight="1">
       <c r="A132" s="16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6566,8 +6887,8 @@
       <c r="M138" s="15" t="n"/>
       <c r="N138" s="15" t="n"/>
     </row>
-    <row r="139" ht="6" customHeight="1"/>
-    <row r="140">
+    <row r="139" ht="18" customHeight="1"/>
+    <row r="140" ht="18" customHeight="1">
       <c r="A140" s="35" t="inlineStr">
         <is>
           <t>COBRANZA ADELANTADA F.</t>
@@ -6587,7 +6908,7 @@
       <c r="M140" s="28" t="n"/>
       <c r="N140" s="28" t="n"/>
     </row>
-    <row r="141" ht="20" customHeight="1">
+    <row r="141" ht="18" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6714,8 +7035,8 @@
       <c r="M147" s="15" t="n"/>
       <c r="N147" s="15" t="n"/>
     </row>
-    <row r="148" ht="6" customHeight="1"/>
-    <row r="149">
+    <row r="148" ht="18" customHeight="1"/>
+    <row r="149" ht="18" customHeight="1">
       <c r="A149" s="82" t="inlineStr">
         <is>
           <t>PROYECCIÓN FEBRERO → FEBRERO</t>
@@ -6735,7 +7056,7 @@
       <c r="M149" s="28" t="n"/>
       <c r="N149" s="28" t="n"/>
     </row>
-    <row r="150">
+    <row r="150" ht="18" customHeight="1">
       <c r="A150" s="19" t="inlineStr">
         <is>
           <t>Proyección FEBRERO</t>
@@ -6743,16 +7064,17 @@
       </c>
       <c r="B150" s="20" t="n"/>
     </row>
-    <row r="152" ht="14" customHeight="1"/>
-    <row r="153" ht="22" customHeight="1">
-      <c r="A153" s="4" t="inlineStr">
+    <row r="151" ht="18" customHeight="1"/>
+    <row r="152" ht="18" customHeight="1"/>
+    <row r="153" ht="24" customHeight="1">
+      <c r="A153" s="277" t="inlineStr">
         <is>
           <t>MARZO 2026</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="28" customHeight="1">
-      <c r="A154" s="5" t="inlineStr">
+    <row r="154" ht="18" customHeight="1">
+      <c r="A154" s="278" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
         </is>
@@ -6818,8 +7140,8 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="35" t="inlineStr">
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="279" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
@@ -6838,8 +7160,8 @@
       <c r="M155" s="28" t="n"/>
       <c r="N155" s="28" t="n"/>
     </row>
-    <row r="156">
-      <c r="A156" s="8" t="inlineStr">
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="278" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
@@ -6860,8 +7182,8 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="8" t="inlineStr">
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="278" t="inlineStr">
         <is>
           <t>Fecha de corte</t>
         </is>
@@ -6874,8 +7196,8 @@
       </c>
       <c r="F157" s="10" t="n"/>
     </row>
-    <row r="158">
-      <c r="A158" s="8" t="inlineStr">
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="278" t="inlineStr">
         <is>
           <t>Reportado por</t>
         </is>
@@ -6888,9 +7210,9 @@
       </c>
       <c r="F158" s="10" t="n"/>
     </row>
-    <row r="159" ht="6" customHeight="1"/>
-    <row r="160">
-      <c r="A160" s="35" t="inlineStr">
+    <row r="159" ht="18" customHeight="1"/>
+    <row r="160" ht="18" customHeight="1">
+      <c r="A160" s="280" t="inlineStr">
         <is>
           <t>COBRANZA CORRIENTE</t>
         </is>
@@ -6909,25 +7231,27 @@
       <c r="M160" s="28" t="n"/>
       <c r="N160" s="28" t="n"/>
     </row>
-    <row r="161" ht="20" customHeight="1">
-      <c r="A161" s="8" t="inlineStr">
+    <row r="161" ht="18" customHeight="1">
+      <c r="A161" s="281" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B161" s="11" t="n"/>
+      <c r="B161" s="282" t="n">
+        <v>1503969</v>
+      </c>
     </row>
     <row r="162" ht="18" customHeight="1">
-      <c r="A162" s="12" t="inlineStr">
+      <c r="A162" s="283" t="inlineStr">
         <is>
           <t>Top 5</t>
         </is>
       </c>
-      <c r="C162" s="13" t="n"/>
-      <c r="D162" s="13" t="n"/>
-      <c r="E162" s="13" t="n"/>
-      <c r="F162" s="13" t="n"/>
-      <c r="G162" s="13" t="n"/>
+      <c r="C162" s="284" t="n"/>
+      <c r="D162" s="284" t="n"/>
+      <c r="E162" s="284" t="n"/>
+      <c r="F162" s="284" t="n"/>
+      <c r="G162" s="284" t="n"/>
       <c r="H162" s="13" t="n"/>
       <c r="I162" s="13" t="n"/>
       <c r="J162" s="13" t="n"/>
@@ -6937,17 +7261,23 @@
       <c r="N162" s="13" t="n"/>
     </row>
     <row r="163" ht="18" customHeight="1">
-      <c r="A163" s="14" t="inlineStr">
-        <is>
-          <t>1er lugar</t>
-        </is>
-      </c>
-      <c r="B163" s="15" t="n"/>
-      <c r="C163" s="15" t="n"/>
-      <c r="D163" s="15" t="n"/>
-      <c r="E163" s="15" t="n"/>
-      <c r="F163" s="15" t="n"/>
-      <c r="G163" s="15" t="n"/>
+      <c r="A163" s="285" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="B163" s="286" t="n">
+        <v>324822</v>
+      </c>
+      <c r="C163" s="287" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="D163" s="287" t="n"/>
+      <c r="E163" s="287" t="n"/>
+      <c r="F163" s="287" t="n"/>
+      <c r="G163" s="287" t="n"/>
       <c r="H163" s="15" t="n"/>
       <c r="I163" s="15" t="n"/>
       <c r="J163" s="15" t="n"/>
@@ -6957,17 +7287,23 @@
       <c r="N163" s="15" t="n"/>
     </row>
     <row r="164" ht="18" customHeight="1">
-      <c r="A164" s="14" t="inlineStr">
-        <is>
-          <t>2o lugar</t>
-        </is>
-      </c>
-      <c r="B164" s="15" t="n"/>
-      <c r="C164" s="15" t="n"/>
-      <c r="D164" s="15" t="n"/>
-      <c r="E164" s="15" t="n"/>
-      <c r="F164" s="15" t="n"/>
-      <c r="G164" s="15" t="n"/>
+      <c r="A164" s="285" t="inlineStr">
+        <is>
+          <t>2o</t>
+        </is>
+      </c>
+      <c r="B164" s="286" t="n">
+        <v>293341</v>
+      </c>
+      <c r="C164" s="287" t="n"/>
+      <c r="D164" s="287" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="E164" s="287" t="n"/>
+      <c r="F164" s="287" t="n"/>
+      <c r="G164" s="287" t="n"/>
       <c r="H164" s="15" t="n"/>
       <c r="I164" s="15" t="n"/>
       <c r="J164" s="15" t="n"/>
@@ -6977,17 +7313,23 @@
       <c r="N164" s="15" t="n"/>
     </row>
     <row r="165" ht="18" customHeight="1">
-      <c r="A165" s="14" t="inlineStr">
-        <is>
-          <t>3er lugar</t>
-        </is>
-      </c>
-      <c r="B165" s="15" t="n"/>
-      <c r="C165" s="15" t="n"/>
-      <c r="D165" s="15" t="n"/>
-      <c r="E165" s="15" t="n"/>
-      <c r="F165" s="15" t="n"/>
-      <c r="G165" s="15" t="n"/>
+      <c r="A165" s="285" t="inlineStr">
+        <is>
+          <t>3er</t>
+        </is>
+      </c>
+      <c r="B165" s="286" t="n">
+        <v>193535</v>
+      </c>
+      <c r="C165" s="287" t="n"/>
+      <c r="D165" s="287" t="n"/>
+      <c r="E165" s="287" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
+      <c r="F165" s="287" t="n"/>
+      <c r="G165" s="287" t="n"/>
       <c r="H165" s="15" t="n"/>
       <c r="I165" s="15" t="n"/>
       <c r="J165" s="15" t="n"/>
@@ -6997,17 +7339,23 @@
       <c r="N165" s="15" t="n"/>
     </row>
     <row r="166" ht="18" customHeight="1">
-      <c r="A166" s="14" t="inlineStr">
-        <is>
-          <t>4o lugar</t>
-        </is>
-      </c>
-      <c r="B166" s="15" t="n"/>
-      <c r="C166" s="15" t="n"/>
-      <c r="D166" s="15" t="n"/>
-      <c r="E166" s="15" t="n"/>
-      <c r="F166" s="15" t="n"/>
-      <c r="G166" s="15" t="n"/>
+      <c r="A166" s="285" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="B166" s="286" t="n">
+        <v>175043</v>
+      </c>
+      <c r="C166" s="287" t="n"/>
+      <c r="D166" s="287" t="n"/>
+      <c r="E166" s="287" t="n"/>
+      <c r="F166" s="287" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="G166" s="287" t="n"/>
       <c r="H166" s="15" t="n"/>
       <c r="I166" s="15" t="n"/>
       <c r="J166" s="15" t="n"/>
@@ -7017,17 +7365,23 @@
       <c r="N166" s="15" t="n"/>
     </row>
     <row r="167" ht="18" customHeight="1">
-      <c r="A167" s="14" t="inlineStr">
-        <is>
-          <t>5o lugar</t>
-        </is>
-      </c>
-      <c r="B167" s="15" t="n"/>
-      <c r="C167" s="15" t="n"/>
-      <c r="D167" s="15" t="n"/>
-      <c r="E167" s="15" t="n"/>
-      <c r="F167" s="15" t="n"/>
-      <c r="G167" s="15" t="n"/>
+      <c r="A167" s="285" t="inlineStr">
+        <is>
+          <t>5o</t>
+        </is>
+      </c>
+      <c r="B167" s="286" t="n">
+        <v>126905</v>
+      </c>
+      <c r="C167" s="287" t="n"/>
+      <c r="D167" s="287" t="n"/>
+      <c r="E167" s="287" t="n"/>
+      <c r="F167" s="287" t="n"/>
+      <c r="G167" s="287" t="inlineStr">
+        <is>
+          <t>V27</t>
+        </is>
+      </c>
       <c r="H167" s="15" t="n"/>
       <c r="I167" s="15" t="n"/>
       <c r="J167" s="15" t="n"/>
@@ -7036,9 +7390,9 @@
       <c r="M167" s="15" t="n"/>
       <c r="N167" s="15" t="n"/>
     </row>
-    <row r="168" ht="6" customHeight="1"/>
-    <row r="169">
-      <c r="A169" s="35" t="inlineStr">
+    <row r="168" ht="18" customHeight="1"/>
+    <row r="169" ht="18" customHeight="1">
+      <c r="A169" s="280" t="inlineStr">
         <is>
           <t>CANCELACIONES</t>
         </is>
@@ -7057,25 +7411,27 @@
       <c r="M169" s="28" t="n"/>
       <c r="N169" s="28" t="n"/>
     </row>
-    <row r="170" ht="20" customHeight="1">
-      <c r="A170" s="16" t="inlineStr">
+    <row r="170" ht="18" customHeight="1">
+      <c r="A170" s="281" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B170" s="17" t="n"/>
+      <c r="B170" s="282" t="n">
+        <v>106825</v>
+      </c>
     </row>
     <row r="171" ht="18" customHeight="1">
-      <c r="A171" s="12" t="inlineStr">
+      <c r="A171" s="283" t="inlineStr">
         <is>
           <t>Top 5</t>
         </is>
       </c>
-      <c r="C171" s="13" t="n"/>
-      <c r="D171" s="13" t="n"/>
-      <c r="E171" s="13" t="n"/>
-      <c r="F171" s="13" t="n"/>
-      <c r="G171" s="13" t="n"/>
+      <c r="C171" s="284" t="n"/>
+      <c r="D171" s="284" t="n"/>
+      <c r="E171" s="284" t="n"/>
+      <c r="F171" s="284" t="n"/>
+      <c r="G171" s="284" t="n"/>
       <c r="H171" s="13" t="n"/>
       <c r="I171" s="13" t="n"/>
       <c r="J171" s="13" t="n"/>
@@ -7085,17 +7441,23 @@
       <c r="N171" s="13" t="n"/>
     </row>
     <row r="172" ht="18" customHeight="1">
-      <c r="A172" s="14" t="inlineStr">
-        <is>
-          <t>1er lugar</t>
-        </is>
-      </c>
-      <c r="B172" s="15" t="n"/>
-      <c r="C172" s="15" t="n"/>
-      <c r="D172" s="15" t="n"/>
-      <c r="E172" s="15" t="n"/>
-      <c r="F172" s="15" t="n"/>
-      <c r="G172" s="15" t="n"/>
+      <c r="A172" s="285" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="B172" s="286" t="n">
+        <v>19788</v>
+      </c>
+      <c r="C172" s="287" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="D172" s="287" t="n"/>
+      <c r="E172" s="287" t="n"/>
+      <c r="F172" s="287" t="n"/>
+      <c r="G172" s="287" t="n"/>
       <c r="H172" s="15" t="n"/>
       <c r="I172" s="15" t="n"/>
       <c r="J172" s="15" t="n"/>
@@ -7105,17 +7467,23 @@
       <c r="N172" s="15" t="n"/>
     </row>
     <row r="173" ht="18" customHeight="1">
-      <c r="A173" s="14" t="inlineStr">
-        <is>
-          <t>2o lugar</t>
-        </is>
-      </c>
-      <c r="B173" s="15" t="n"/>
-      <c r="C173" s="15" t="n"/>
-      <c r="D173" s="15" t="n"/>
-      <c r="E173" s="15" t="n"/>
-      <c r="F173" s="15" t="n"/>
-      <c r="G173" s="15" t="n"/>
+      <c r="A173" s="285" t="inlineStr">
+        <is>
+          <t>2o</t>
+        </is>
+      </c>
+      <c r="B173" s="286" t="n">
+        <v>16551</v>
+      </c>
+      <c r="C173" s="287" t="n"/>
+      <c r="D173" s="287" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
+      <c r="E173" s="287" t="n"/>
+      <c r="F173" s="287" t="n"/>
+      <c r="G173" s="287" t="n"/>
       <c r="H173" s="15" t="n"/>
       <c r="I173" s="15" t="n"/>
       <c r="J173" s="15" t="n"/>
@@ -7125,17 +7493,23 @@
       <c r="N173" s="15" t="n"/>
     </row>
     <row r="174" ht="18" customHeight="1">
-      <c r="A174" s="14" t="inlineStr">
-        <is>
-          <t>3er lugar</t>
-        </is>
-      </c>
-      <c r="B174" s="15" t="n"/>
-      <c r="C174" s="15" t="n"/>
-      <c r="D174" s="15" t="n"/>
-      <c r="E174" s="15" t="n"/>
-      <c r="F174" s="15" t="n"/>
-      <c r="G174" s="15" t="n"/>
+      <c r="A174" s="285" t="inlineStr">
+        <is>
+          <t>3er</t>
+        </is>
+      </c>
+      <c r="B174" s="286" t="n">
+        <v>15166</v>
+      </c>
+      <c r="C174" s="287" t="n"/>
+      <c r="D174" s="287" t="n"/>
+      <c r="E174" s="287" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="F174" s="287" t="n"/>
+      <c r="G174" s="287" t="n"/>
       <c r="H174" s="15" t="n"/>
       <c r="I174" s="15" t="n"/>
       <c r="J174" s="15" t="n"/>
@@ -7145,17 +7519,23 @@
       <c r="N174" s="15" t="n"/>
     </row>
     <row r="175" ht="18" customHeight="1">
-      <c r="A175" s="14" t="inlineStr">
-        <is>
-          <t>4o lugar</t>
-        </is>
-      </c>
-      <c r="B175" s="15" t="n"/>
-      <c r="C175" s="15" t="n"/>
-      <c r="D175" s="15" t="n"/>
-      <c r="E175" s="15" t="n"/>
-      <c r="F175" s="15" t="n"/>
-      <c r="G175" s="15" t="n"/>
+      <c r="A175" s="285" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="B175" s="286" t="n">
+        <v>13415</v>
+      </c>
+      <c r="C175" s="287" t="n"/>
+      <c r="D175" s="287" t="n"/>
+      <c r="E175" s="287" t="n"/>
+      <c r="F175" s="287" t="inlineStr">
+        <is>
+          <t>V56</t>
+        </is>
+      </c>
+      <c r="G175" s="287" t="n"/>
       <c r="H175" s="15" t="n"/>
       <c r="I175" s="15" t="n"/>
       <c r="J175" s="15" t="n"/>
@@ -7165,17 +7545,23 @@
       <c r="N175" s="15" t="n"/>
     </row>
     <row r="176" ht="18" customHeight="1">
-      <c r="A176" s="14" t="inlineStr">
-        <is>
-          <t>5o lugar</t>
-        </is>
-      </c>
-      <c r="B176" s="15" t="n"/>
-      <c r="C176" s="15" t="n"/>
-      <c r="D176" s="15" t="n"/>
-      <c r="E176" s="15" t="n"/>
-      <c r="F176" s="15" t="n"/>
-      <c r="G176" s="15" t="n"/>
+      <c r="A176" s="285" t="inlineStr">
+        <is>
+          <t>5o</t>
+        </is>
+      </c>
+      <c r="B176" s="286" t="n">
+        <v>12616</v>
+      </c>
+      <c r="C176" s="287" t="n"/>
+      <c r="D176" s="287" t="n"/>
+      <c r="E176" s="287" t="n"/>
+      <c r="F176" s="287" t="n"/>
+      <c r="G176" s="287" t="inlineStr">
+        <is>
+          <t>V84</t>
+        </is>
+      </c>
       <c r="H176" s="15" t="n"/>
       <c r="I176" s="15" t="n"/>
       <c r="J176" s="15" t="n"/>
@@ -7184,9 +7570,9 @@
       <c r="M176" s="15" t="n"/>
       <c r="N176" s="15" t="n"/>
     </row>
-    <row r="177" ht="6" customHeight="1"/>
-    <row r="178">
-      <c r="A178" s="35" t="inlineStr">
+    <row r="177" ht="18" customHeight="1"/>
+    <row r="178" ht="18" customHeight="1">
+      <c r="A178" s="280" t="inlineStr">
         <is>
           <t>COBRANZA VENCIDA</t>
         </is>
@@ -7205,25 +7591,27 @@
       <c r="M178" s="28" t="n"/>
       <c r="N178" s="28" t="n"/>
     </row>
-    <row r="179" ht="20" customHeight="1">
-      <c r="A179" s="8" t="inlineStr">
+    <row r="179" ht="18" customHeight="1">
+      <c r="A179" s="281" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B179" s="11" t="n"/>
+      <c r="B179" s="282" t="n">
+        <v>145938</v>
+      </c>
     </row>
     <row r="180" ht="18" customHeight="1">
-      <c r="A180" s="12" t="inlineStr">
+      <c r="A180" s="283" t="inlineStr">
         <is>
           <t>Top 5</t>
         </is>
       </c>
-      <c r="C180" s="13" t="n"/>
-      <c r="D180" s="13" t="n"/>
-      <c r="E180" s="13" t="n"/>
-      <c r="F180" s="13" t="n"/>
-      <c r="G180" s="13" t="n"/>
+      <c r="C180" s="284" t="n"/>
+      <c r="D180" s="284" t="n"/>
+      <c r="E180" s="284" t="n"/>
+      <c r="F180" s="284" t="n"/>
+      <c r="G180" s="284" t="n"/>
       <c r="H180" s="13" t="n"/>
       <c r="I180" s="13" t="n"/>
       <c r="J180" s="13" t="n"/>
@@ -7233,17 +7621,23 @@
       <c r="N180" s="13" t="n"/>
     </row>
     <row r="181" ht="18" customHeight="1">
-      <c r="A181" s="14" t="inlineStr">
-        <is>
-          <t>1er lugar</t>
-        </is>
-      </c>
-      <c r="B181" s="15" t="n"/>
-      <c r="C181" s="15" t="n"/>
-      <c r="D181" s="15" t="n"/>
-      <c r="E181" s="15" t="n"/>
-      <c r="F181" s="15" t="n"/>
-      <c r="G181" s="15" t="n"/>
+      <c r="A181" s="285" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="B181" s="286" t="n">
+        <v>30632</v>
+      </c>
+      <c r="C181" s="287" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="D181" s="287" t="n"/>
+      <c r="E181" s="287" t="n"/>
+      <c r="F181" s="287" t="n"/>
+      <c r="G181" s="287" t="n"/>
       <c r="H181" s="15" t="n"/>
       <c r="I181" s="15" t="n"/>
       <c r="J181" s="15" t="n"/>
@@ -7253,17 +7647,23 @@
       <c r="N181" s="15" t="n"/>
     </row>
     <row r="182" ht="18" customHeight="1">
-      <c r="A182" s="14" t="inlineStr">
-        <is>
-          <t>2o lugar</t>
-        </is>
-      </c>
-      <c r="B182" s="15" t="n"/>
-      <c r="C182" s="15" t="n"/>
-      <c r="D182" s="15" t="n"/>
-      <c r="E182" s="15" t="n"/>
-      <c r="F182" s="15" t="n"/>
-      <c r="G182" s="15" t="n"/>
+      <c r="A182" s="285" t="inlineStr">
+        <is>
+          <t>2o</t>
+        </is>
+      </c>
+      <c r="B182" s="286" t="n">
+        <v>23081</v>
+      </c>
+      <c r="C182" s="287" t="n"/>
+      <c r="D182" s="287" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="E182" s="287" t="n"/>
+      <c r="F182" s="287" t="n"/>
+      <c r="G182" s="287" t="n"/>
       <c r="H182" s="15" t="n"/>
       <c r="I182" s="15" t="n"/>
       <c r="J182" s="15" t="n"/>
@@ -7273,17 +7673,23 @@
       <c r="N182" s="15" t="n"/>
     </row>
     <row r="183" ht="18" customHeight="1">
-      <c r="A183" s="14" t="inlineStr">
-        <is>
-          <t>3er lugar</t>
-        </is>
-      </c>
-      <c r="B183" s="15" t="n"/>
-      <c r="C183" s="15" t="n"/>
-      <c r="D183" s="15" t="n"/>
-      <c r="E183" s="15" t="n"/>
-      <c r="F183" s="15" t="n"/>
-      <c r="G183" s="15" t="n"/>
+      <c r="A183" s="285" t="inlineStr">
+        <is>
+          <t>3er</t>
+        </is>
+      </c>
+      <c r="B183" s="286" t="n">
+        <v>22118</v>
+      </c>
+      <c r="C183" s="287" t="n"/>
+      <c r="D183" s="287" t="n"/>
+      <c r="E183" s="287" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="F183" s="287" t="n"/>
+      <c r="G183" s="287" t="n"/>
       <c r="H183" s="15" t="n"/>
       <c r="I183" s="15" t="n"/>
       <c r="J183" s="15" t="n"/>
@@ -7293,17 +7699,23 @@
       <c r="N183" s="15" t="n"/>
     </row>
     <row r="184" ht="18" customHeight="1">
-      <c r="A184" s="14" t="inlineStr">
-        <is>
-          <t>4o lugar</t>
-        </is>
-      </c>
-      <c r="B184" s="15" t="n"/>
-      <c r="C184" s="15" t="n"/>
-      <c r="D184" s="15" t="n"/>
-      <c r="E184" s="15" t="n"/>
-      <c r="F184" s="15" t="n"/>
-      <c r="G184" s="15" t="n"/>
+      <c r="A184" s="285" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="B184" s="286" t="n">
+        <v>21557</v>
+      </c>
+      <c r="C184" s="287" t="n"/>
+      <c r="D184" s="287" t="n"/>
+      <c r="E184" s="287" t="n"/>
+      <c r="F184" s="287" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="G184" s="287" t="n"/>
       <c r="H184" s="15" t="n"/>
       <c r="I184" s="15" t="n"/>
       <c r="J184" s="15" t="n"/>
@@ -7313,17 +7725,23 @@
       <c r="N184" s="15" t="n"/>
     </row>
     <row r="185" ht="18" customHeight="1">
-      <c r="A185" s="14" t="inlineStr">
-        <is>
-          <t>5o lugar</t>
-        </is>
-      </c>
-      <c r="B185" s="15" t="n"/>
-      <c r="C185" s="15" t="n"/>
-      <c r="D185" s="15" t="n"/>
-      <c r="E185" s="15" t="n"/>
-      <c r="F185" s="15" t="n"/>
-      <c r="G185" s="15" t="n"/>
+      <c r="A185" s="285" t="inlineStr">
+        <is>
+          <t>5o</t>
+        </is>
+      </c>
+      <c r="B185" s="286" t="n">
+        <v>12381</v>
+      </c>
+      <c r="C185" s="287" t="n"/>
+      <c r="D185" s="287" t="n"/>
+      <c r="E185" s="287" t="n"/>
+      <c r="F185" s="287" t="n"/>
+      <c r="G185" s="287" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
       <c r="H185" s="15" t="n"/>
       <c r="I185" s="15" t="n"/>
       <c r="J185" s="15" t="n"/>
@@ -7332,9 +7750,9 @@
       <c r="M185" s="15" t="n"/>
       <c r="N185" s="15" t="n"/>
     </row>
-    <row r="186" ht="6" customHeight="1"/>
-    <row r="187">
-      <c r="A187" s="35" t="inlineStr">
+    <row r="186" ht="18" customHeight="1"/>
+    <row r="187" ht="18" customHeight="1">
+      <c r="A187" s="280" t="inlineStr">
         <is>
           <t>COBRANZA EFECTIVA</t>
         </is>
@@ -7353,25 +7771,27 @@
       <c r="M187" s="28" t="n"/>
       <c r="N187" s="28" t="n"/>
     </row>
-    <row r="188" ht="20" customHeight="1">
-      <c r="A188" s="16" t="inlineStr">
+    <row r="188" ht="18" customHeight="1">
+      <c r="A188" s="281" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B188" s="17" t="n"/>
+      <c r="B188" s="282" t="n">
+        <v>1202393</v>
+      </c>
     </row>
     <row r="189" ht="18" customHeight="1">
-      <c r="A189" s="12" t="inlineStr">
+      <c r="A189" s="283" t="inlineStr">
         <is>
           <t>Top 5</t>
         </is>
       </c>
-      <c r="C189" s="13" t="n"/>
-      <c r="D189" s="13" t="n"/>
-      <c r="E189" s="13" t="n"/>
-      <c r="F189" s="13" t="n"/>
-      <c r="G189" s="13" t="n"/>
+      <c r="C189" s="284" t="n"/>
+      <c r="D189" s="284" t="n"/>
+      <c r="E189" s="284" t="n"/>
+      <c r="F189" s="284" t="n"/>
+      <c r="G189" s="284" t="n"/>
       <c r="H189" s="13" t="n"/>
       <c r="I189" s="13" t="n"/>
       <c r="J189" s="13" t="n"/>
@@ -7381,17 +7801,23 @@
       <c r="N189" s="13" t="n"/>
     </row>
     <row r="190" ht="18" customHeight="1">
-      <c r="A190" s="14" t="inlineStr">
-        <is>
-          <t>1er lugar</t>
-        </is>
-      </c>
-      <c r="B190" s="15" t="n"/>
-      <c r="C190" s="15" t="n"/>
-      <c r="D190" s="15" t="n"/>
-      <c r="E190" s="15" t="n"/>
-      <c r="F190" s="15" t="n"/>
-      <c r="G190" s="15" t="n"/>
+      <c r="A190" s="285" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="B190" s="286" t="n">
+        <v>199444</v>
+      </c>
+      <c r="C190" s="287" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D190" s="287" t="n"/>
+      <c r="E190" s="287" t="n"/>
+      <c r="F190" s="287" t="n"/>
+      <c r="G190" s="287" t="n"/>
       <c r="H190" s="15" t="n"/>
       <c r="I190" s="15" t="n"/>
       <c r="J190" s="15" t="n"/>
@@ -7401,17 +7827,23 @@
       <c r="N190" s="15" t="n"/>
     </row>
     <row r="191" ht="18" customHeight="1">
-      <c r="A191" s="14" t="inlineStr">
-        <is>
-          <t>2o lugar</t>
-        </is>
-      </c>
-      <c r="B191" s="15" t="n"/>
-      <c r="C191" s="15" t="n"/>
-      <c r="D191" s="15" t="n"/>
-      <c r="E191" s="15" t="n"/>
-      <c r="F191" s="15" t="n"/>
-      <c r="G191" s="15" t="n"/>
+      <c r="A191" s="285" t="inlineStr">
+        <is>
+          <t>2o</t>
+        </is>
+      </c>
+      <c r="B191" s="286" t="n">
+        <v>168196</v>
+      </c>
+      <c r="C191" s="287" t="n"/>
+      <c r="D191" s="287" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="E191" s="287" t="n"/>
+      <c r="F191" s="287" t="n"/>
+      <c r="G191" s="287" t="n"/>
       <c r="H191" s="15" t="n"/>
       <c r="I191" s="15" t="n"/>
       <c r="J191" s="15" t="n"/>
@@ -7421,17 +7853,23 @@
       <c r="N191" s="15" t="n"/>
     </row>
     <row r="192" ht="18" customHeight="1">
-      <c r="A192" s="14" t="inlineStr">
-        <is>
-          <t>3er lugar</t>
-        </is>
-      </c>
-      <c r="B192" s="15" t="n"/>
-      <c r="C192" s="15" t="n"/>
-      <c r="D192" s="15" t="n"/>
-      <c r="E192" s="15" t="n"/>
-      <c r="F192" s="15" t="n"/>
-      <c r="G192" s="15" t="n"/>
+      <c r="A192" s="285" t="inlineStr">
+        <is>
+          <t>3er</t>
+        </is>
+      </c>
+      <c r="B192" s="286" t="n">
+        <v>118908</v>
+      </c>
+      <c r="C192" s="287" t="n"/>
+      <c r="D192" s="287" t="n"/>
+      <c r="E192" s="287" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="F192" s="287" t="n"/>
+      <c r="G192" s="287" t="n"/>
       <c r="H192" s="15" t="n"/>
       <c r="I192" s="15" t="n"/>
       <c r="J192" s="15" t="n"/>
@@ -7441,17 +7879,23 @@
       <c r="N192" s="15" t="n"/>
     </row>
     <row r="193" ht="18" customHeight="1">
-      <c r="A193" s="14" t="inlineStr">
-        <is>
-          <t>4o lugar</t>
-        </is>
-      </c>
-      <c r="B193" s="15" t="n"/>
-      <c r="C193" s="15" t="n"/>
-      <c r="D193" s="15" t="n"/>
-      <c r="E193" s="15" t="n"/>
-      <c r="F193" s="15" t="n"/>
-      <c r="G193" s="15" t="n"/>
+      <c r="A193" s="285" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="B193" s="286" t="n">
+        <v>113756</v>
+      </c>
+      <c r="C193" s="287" t="n"/>
+      <c r="D193" s="287" t="n"/>
+      <c r="E193" s="287" t="n"/>
+      <c r="F193" s="287" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="G193" s="287" t="n"/>
       <c r="H193" s="15" t="n"/>
       <c r="I193" s="15" t="n"/>
       <c r="J193" s="15" t="n"/>
@@ -7461,17 +7905,23 @@
       <c r="N193" s="15" t="n"/>
     </row>
     <row r="194" ht="18" customHeight="1">
-      <c r="A194" s="14" t="inlineStr">
-        <is>
-          <t>5o lugar</t>
-        </is>
-      </c>
-      <c r="B194" s="15" t="n"/>
-      <c r="C194" s="15" t="n"/>
-      <c r="D194" s="15" t="n"/>
-      <c r="E194" s="15" t="n"/>
-      <c r="F194" s="15" t="n"/>
-      <c r="G194" s="15" t="n"/>
+      <c r="A194" s="285" t="inlineStr">
+        <is>
+          <t>5o</t>
+        </is>
+      </c>
+      <c r="B194" s="286" t="n">
+        <v>95792</v>
+      </c>
+      <c r="C194" s="287" t="n"/>
+      <c r="D194" s="287" t="n"/>
+      <c r="E194" s="287" t="n"/>
+      <c r="F194" s="287" t="n"/>
+      <c r="G194" s="287" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
       <c r="H194" s="15" t="n"/>
       <c r="I194" s="15" t="n"/>
       <c r="J194" s="15" t="n"/>
@@ -7480,9 +7930,9 @@
       <c r="M194" s="15" t="n"/>
       <c r="N194" s="15" t="n"/>
     </row>
-    <row r="195" ht="6" customHeight="1"/>
-    <row r="196">
-      <c r="A196" s="35" t="inlineStr">
+    <row r="195" ht="18" customHeight="1"/>
+    <row r="196" ht="18" customHeight="1">
+      <c r="A196" s="280" t="inlineStr">
         <is>
           <t>COBRANZA RECUPERADA</t>
         </is>
@@ -7501,25 +7951,27 @@
       <c r="M196" s="28" t="n"/>
       <c r="N196" s="28" t="n"/>
     </row>
-    <row r="197" ht="20" customHeight="1">
-      <c r="A197" s="8" t="inlineStr">
+    <row r="197" ht="18" customHeight="1">
+      <c r="A197" s="281" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B197" s="11" t="n"/>
+      <c r="B197" s="282" t="n">
+        <v>180788</v>
+      </c>
     </row>
     <row r="198" ht="18" customHeight="1">
-      <c r="A198" s="12" t="inlineStr">
+      <c r="A198" s="283" t="inlineStr">
         <is>
           <t>Top 5</t>
         </is>
       </c>
-      <c r="C198" s="13" t="n"/>
-      <c r="D198" s="13" t="n"/>
-      <c r="E198" s="13" t="n"/>
-      <c r="F198" s="13" t="n"/>
-      <c r="G198" s="13" t="n"/>
+      <c r="C198" s="284" t="n"/>
+      <c r="D198" s="284" t="n"/>
+      <c r="E198" s="284" t="n"/>
+      <c r="F198" s="284" t="n"/>
+      <c r="G198" s="284" t="n"/>
       <c r="H198" s="13" t="n"/>
       <c r="I198" s="13" t="n"/>
       <c r="J198" s="13" t="n"/>
@@ -7529,17 +7981,23 @@
       <c r="N198" s="13" t="n"/>
     </row>
     <row r="199" ht="18" customHeight="1">
-      <c r="A199" s="14" t="inlineStr">
-        <is>
-          <t>1er lugar</t>
-        </is>
-      </c>
-      <c r="B199" s="15" t="n"/>
-      <c r="C199" s="15" t="n"/>
-      <c r="D199" s="15" t="n"/>
-      <c r="E199" s="15" t="n"/>
-      <c r="F199" s="15" t="n"/>
-      <c r="G199" s="15" t="n"/>
+      <c r="A199" s="285" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="B199" s="286" t="n">
+        <v>39900</v>
+      </c>
+      <c r="C199" s="287" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="D199" s="287" t="n"/>
+      <c r="E199" s="287" t="n"/>
+      <c r="F199" s="287" t="n"/>
+      <c r="G199" s="287" t="n"/>
       <c r="H199" s="15" t="n"/>
       <c r="I199" s="15" t="n"/>
       <c r="J199" s="15" t="n"/>
@@ -7549,17 +8007,23 @@
       <c r="N199" s="15" t="n"/>
     </row>
     <row r="200" ht="18" customHeight="1">
-      <c r="A200" s="14" t="inlineStr">
-        <is>
-          <t>2o lugar</t>
-        </is>
-      </c>
-      <c r="B200" s="15" t="n"/>
-      <c r="C200" s="15" t="n"/>
-      <c r="D200" s="15" t="n"/>
-      <c r="E200" s="15" t="n"/>
-      <c r="F200" s="15" t="n"/>
-      <c r="G200" s="15" t="n"/>
+      <c r="A200" s="285" t="inlineStr">
+        <is>
+          <t>2o</t>
+        </is>
+      </c>
+      <c r="B200" s="286" t="n">
+        <v>30129</v>
+      </c>
+      <c r="C200" s="287" t="n"/>
+      <c r="D200" s="287" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="E200" s="287" t="n"/>
+      <c r="F200" s="287" t="n"/>
+      <c r="G200" s="287" t="n"/>
       <c r="H200" s="15" t="n"/>
       <c r="I200" s="15" t="n"/>
       <c r="J200" s="15" t="n"/>
@@ -7569,17 +8033,23 @@
       <c r="N200" s="15" t="n"/>
     </row>
     <row r="201" ht="18" customHeight="1">
-      <c r="A201" s="14" t="inlineStr">
-        <is>
-          <t>3er lugar</t>
-        </is>
-      </c>
-      <c r="B201" s="15" t="n"/>
-      <c r="C201" s="15" t="n"/>
-      <c r="D201" s="15" t="n"/>
-      <c r="E201" s="15" t="n"/>
-      <c r="F201" s="15" t="n"/>
-      <c r="G201" s="15" t="n"/>
+      <c r="A201" s="285" t="inlineStr">
+        <is>
+          <t>3er</t>
+        </is>
+      </c>
+      <c r="B201" s="286" t="n">
+        <v>28947</v>
+      </c>
+      <c r="C201" s="287" t="n"/>
+      <c r="D201" s="287" t="n"/>
+      <c r="E201" s="287" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="F201" s="287" t="n"/>
+      <c r="G201" s="287" t="n"/>
       <c r="H201" s="15" t="n"/>
       <c r="I201" s="15" t="n"/>
       <c r="J201" s="15" t="n"/>
@@ -7589,17 +8059,23 @@
       <c r="N201" s="15" t="n"/>
     </row>
     <row r="202" ht="18" customHeight="1">
-      <c r="A202" s="14" t="inlineStr">
-        <is>
-          <t>4o lugar</t>
-        </is>
-      </c>
-      <c r="B202" s="15" t="n"/>
-      <c r="C202" s="15" t="n"/>
-      <c r="D202" s="15" t="n"/>
-      <c r="E202" s="15" t="n"/>
-      <c r="F202" s="15" t="n"/>
-      <c r="G202" s="15" t="n"/>
+      <c r="A202" s="285" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="B202" s="286" t="n">
+        <v>22542</v>
+      </c>
+      <c r="C202" s="287" t="n"/>
+      <c r="D202" s="287" t="n"/>
+      <c r="E202" s="287" t="n"/>
+      <c r="F202" s="287" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="G202" s="287" t="n"/>
       <c r="H202" s="15" t="n"/>
       <c r="I202" s="15" t="n"/>
       <c r="J202" s="15" t="n"/>
@@ -7609,17 +8085,23 @@
       <c r="N202" s="15" t="n"/>
     </row>
     <row r="203" ht="18" customHeight="1">
-      <c r="A203" s="14" t="inlineStr">
-        <is>
-          <t>5o lugar</t>
-        </is>
-      </c>
-      <c r="B203" s="15" t="n"/>
-      <c r="C203" s="15" t="n"/>
-      <c r="D203" s="15" t="n"/>
-      <c r="E203" s="15" t="n"/>
-      <c r="F203" s="15" t="n"/>
-      <c r="G203" s="15" t="n"/>
+      <c r="A203" s="285" t="inlineStr">
+        <is>
+          <t>5o</t>
+        </is>
+      </c>
+      <c r="B203" s="286" t="n">
+        <v>13930</v>
+      </c>
+      <c r="C203" s="287" t="n"/>
+      <c r="D203" s="287" t="n"/>
+      <c r="E203" s="287" t="n"/>
+      <c r="F203" s="287" t="n"/>
+      <c r="G203" s="287" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
       <c r="H203" s="15" t="n"/>
       <c r="I203" s="15" t="n"/>
       <c r="J203" s="15" t="n"/>
@@ -7628,9 +8110,9 @@
       <c r="M203" s="15" t="n"/>
       <c r="N203" s="15" t="n"/>
     </row>
-    <row r="204" ht="6" customHeight="1"/>
-    <row r="205">
-      <c r="A205" s="35" t="inlineStr">
+    <row r="204" ht="18" customHeight="1"/>
+    <row r="205" ht="18" customHeight="1">
+      <c r="A205" s="280" t="inlineStr">
         <is>
           <t>COBRANZA TOTAL GENERAL</t>
         </is>
@@ -7649,25 +8131,27 @@
       <c r="M205" s="28" t="n"/>
       <c r="N205" s="28" t="n"/>
     </row>
-    <row r="206" ht="20" customHeight="1">
-      <c r="A206" s="16" t="inlineStr">
+    <row r="206" ht="18" customHeight="1">
+      <c r="A206" s="281" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B206" s="17" t="n"/>
+      <c r="B206" s="282" t="n">
+        <v>1433162</v>
+      </c>
     </row>
     <row r="207" ht="18" customHeight="1">
-      <c r="A207" s="12" t="inlineStr">
+      <c r="A207" s="283" t="inlineStr">
         <is>
           <t>Top 5</t>
         </is>
       </c>
-      <c r="C207" s="13" t="n"/>
-      <c r="D207" s="13" t="n"/>
-      <c r="E207" s="13" t="n"/>
-      <c r="F207" s="13" t="n"/>
-      <c r="G207" s="13" t="n"/>
+      <c r="C207" s="284" t="n"/>
+      <c r="D207" s="284" t="n"/>
+      <c r="E207" s="284" t="n"/>
+      <c r="F207" s="284" t="n"/>
+      <c r="G207" s="284" t="n"/>
       <c r="H207" s="13" t="n"/>
       <c r="I207" s="13" t="n"/>
       <c r="J207" s="13" t="n"/>
@@ -7677,17 +8161,23 @@
       <c r="N207" s="13" t="n"/>
     </row>
     <row r="208" ht="18" customHeight="1">
-      <c r="A208" s="14" t="inlineStr">
-        <is>
-          <t>1er lugar</t>
-        </is>
-      </c>
-      <c r="B208" s="15" t="n"/>
-      <c r="C208" s="15" t="n"/>
-      <c r="D208" s="15" t="n"/>
-      <c r="E208" s="15" t="n"/>
-      <c r="F208" s="15" t="n"/>
-      <c r="G208" s="15" t="n"/>
+      <c r="A208" s="285" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="B208" s="286" t="n">
+        <v>234290</v>
+      </c>
+      <c r="C208" s="287" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D208" s="287" t="n"/>
+      <c r="E208" s="287" t="n"/>
+      <c r="F208" s="287" t="n"/>
+      <c r="G208" s="287" t="n"/>
       <c r="H208" s="15" t="n"/>
       <c r="I208" s="15" t="n"/>
       <c r="J208" s="15" t="n"/>
@@ -7697,17 +8187,23 @@
       <c r="N208" s="15" t="n"/>
     </row>
     <row r="209" ht="18" customHeight="1">
-      <c r="A209" s="14" t="inlineStr">
-        <is>
-          <t>2o lugar</t>
-        </is>
-      </c>
-      <c r="B209" s="15" t="n"/>
-      <c r="C209" s="15" t="n"/>
-      <c r="D209" s="15" t="n"/>
-      <c r="E209" s="15" t="n"/>
-      <c r="F209" s="15" t="n"/>
-      <c r="G209" s="15" t="n"/>
+      <c r="A209" s="285" t="inlineStr">
+        <is>
+          <t>2o</t>
+        </is>
+      </c>
+      <c r="B209" s="286" t="n">
+        <v>196468</v>
+      </c>
+      <c r="C209" s="287" t="n"/>
+      <c r="D209" s="287" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="E209" s="287" t="n"/>
+      <c r="F209" s="287" t="n"/>
+      <c r="G209" s="287" t="n"/>
       <c r="H209" s="15" t="n"/>
       <c r="I209" s="15" t="n"/>
       <c r="J209" s="15" t="n"/>
@@ -7717,17 +8213,23 @@
       <c r="N209" s="15" t="n"/>
     </row>
     <row r="210" ht="18" customHeight="1">
-      <c r="A210" s="14" t="inlineStr">
-        <is>
-          <t>3er lugar</t>
-        </is>
-      </c>
-      <c r="B210" s="15" t="n"/>
-      <c r="C210" s="15" t="n"/>
-      <c r="D210" s="15" t="n"/>
-      <c r="E210" s="15" t="n"/>
-      <c r="F210" s="15" t="n"/>
-      <c r="G210" s="15" t="n"/>
+      <c r="A210" s="285" t="inlineStr">
+        <is>
+          <t>3er</t>
+        </is>
+      </c>
+      <c r="B210" s="286" t="n">
+        <v>143885</v>
+      </c>
+      <c r="C210" s="287" t="n"/>
+      <c r="D210" s="287" t="n"/>
+      <c r="E210" s="287" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="F210" s="287" t="n"/>
+      <c r="G210" s="287" t="n"/>
       <c r="H210" s="15" t="n"/>
       <c r="I210" s="15" t="n"/>
       <c r="J210" s="15" t="n"/>
@@ -7737,17 +8239,23 @@
       <c r="N210" s="15" t="n"/>
     </row>
     <row r="211" ht="18" customHeight="1">
-      <c r="A211" s="14" t="inlineStr">
-        <is>
-          <t>4o lugar</t>
-        </is>
-      </c>
-      <c r="B211" s="15" t="n"/>
-      <c r="C211" s="15" t="n"/>
-      <c r="D211" s="15" t="n"/>
-      <c r="E211" s="15" t="n"/>
-      <c r="F211" s="15" t="n"/>
-      <c r="G211" s="15" t="n"/>
+      <c r="A211" s="285" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="B211" s="286" t="n">
+        <v>129918</v>
+      </c>
+      <c r="C211" s="287" t="n"/>
+      <c r="D211" s="287" t="n"/>
+      <c r="E211" s="287" t="n"/>
+      <c r="F211" s="287" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="G211" s="287" t="n"/>
       <c r="H211" s="15" t="n"/>
       <c r="I211" s="15" t="n"/>
       <c r="J211" s="15" t="n"/>
@@ -7757,17 +8265,23 @@
       <c r="N211" s="15" t="n"/>
     </row>
     <row r="212" ht="18" customHeight="1">
-      <c r="A212" s="14" t="inlineStr">
-        <is>
-          <t>5o lugar</t>
-        </is>
-      </c>
-      <c r="B212" s="15" t="n"/>
-      <c r="C212" s="15" t="n"/>
-      <c r="D212" s="15" t="n"/>
-      <c r="E212" s="15" t="n"/>
-      <c r="F212" s="15" t="n"/>
-      <c r="G212" s="15" t="n"/>
+      <c r="A212" s="285" t="inlineStr">
+        <is>
+          <t>5o</t>
+        </is>
+      </c>
+      <c r="B212" s="286" t="n">
+        <v>119867</v>
+      </c>
+      <c r="C212" s="287" t="n"/>
+      <c r="D212" s="287" t="n"/>
+      <c r="E212" s="287" t="n"/>
+      <c r="F212" s="287" t="n"/>
+      <c r="G212" s="287" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
       <c r="H212" s="15" t="n"/>
       <c r="I212" s="15" t="n"/>
       <c r="J212" s="15" t="n"/>
@@ -7776,9 +8290,9 @@
       <c r="M212" s="15" t="n"/>
       <c r="N212" s="15" t="n"/>
     </row>
-    <row r="213" ht="6" customHeight="1"/>
-    <row r="214">
-      <c r="A214" s="35" t="inlineStr">
+    <row r="213" ht="18" customHeight="1"/>
+    <row r="214" ht="18" customHeight="1">
+      <c r="A214" s="280" t="inlineStr">
         <is>
           <t>COBRANZA ADELANTADA F.</t>
         </is>
@@ -7797,25 +8311,25 @@
       <c r="M214" s="28" t="n"/>
       <c r="N214" s="28" t="n"/>
     </row>
-    <row r="215" ht="20" customHeight="1">
-      <c r="A215" s="8" t="inlineStr">
+    <row r="215" ht="18" customHeight="1">
+      <c r="A215" s="281" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B215" s="11" t="n"/>
+      <c r="B215" s="282" t="n"/>
     </row>
     <row r="216" ht="18" customHeight="1">
-      <c r="A216" s="12" t="inlineStr">
+      <c r="A216" s="283" t="inlineStr">
         <is>
           <t>Top 5</t>
         </is>
       </c>
-      <c r="C216" s="13" t="n"/>
-      <c r="D216" s="13" t="n"/>
-      <c r="E216" s="13" t="n"/>
-      <c r="F216" s="13" t="n"/>
-      <c r="G216" s="13" t="n"/>
+      <c r="C216" s="284" t="n"/>
+      <c r="D216" s="284" t="n"/>
+      <c r="E216" s="284" t="n"/>
+      <c r="F216" s="284" t="n"/>
+      <c r="G216" s="284" t="n"/>
       <c r="H216" s="13" t="n"/>
       <c r="I216" s="13" t="n"/>
       <c r="J216" s="13" t="n"/>
@@ -7825,17 +8339,17 @@
       <c r="N216" s="13" t="n"/>
     </row>
     <row r="217" ht="18" customHeight="1">
-      <c r="A217" s="14" t="inlineStr">
-        <is>
-          <t>1er lugar</t>
-        </is>
-      </c>
-      <c r="B217" s="15" t="n"/>
-      <c r="C217" s="15" t="n"/>
-      <c r="D217" s="15" t="n"/>
-      <c r="E217" s="15" t="n"/>
-      <c r="F217" s="15" t="n"/>
-      <c r="G217" s="15" t="n"/>
+      <c r="A217" s="285" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="B217" s="286" t="n"/>
+      <c r="C217" s="287" t="n"/>
+      <c r="D217" s="287" t="n"/>
+      <c r="E217" s="287" t="n"/>
+      <c r="F217" s="287" t="n"/>
+      <c r="G217" s="287" t="n"/>
       <c r="H217" s="15" t="n"/>
       <c r="I217" s="15" t="n"/>
       <c r="J217" s="15" t="n"/>
@@ -7845,17 +8359,17 @@
       <c r="N217" s="15" t="n"/>
     </row>
     <row r="218" ht="18" customHeight="1">
-      <c r="A218" s="14" t="inlineStr">
-        <is>
-          <t>2o lugar</t>
-        </is>
-      </c>
-      <c r="B218" s="15" t="n"/>
-      <c r="C218" s="15" t="n"/>
-      <c r="D218" s="15" t="n"/>
-      <c r="E218" s="15" t="n"/>
-      <c r="F218" s="15" t="n"/>
-      <c r="G218" s="15" t="n"/>
+      <c r="A218" s="285" t="inlineStr">
+        <is>
+          <t>2o</t>
+        </is>
+      </c>
+      <c r="B218" s="286" t="n"/>
+      <c r="C218" s="287" t="n"/>
+      <c r="D218" s="287" t="n"/>
+      <c r="E218" s="287" t="n"/>
+      <c r="F218" s="287" t="n"/>
+      <c r="G218" s="287" t="n"/>
       <c r="H218" s="15" t="n"/>
       <c r="I218" s="15" t="n"/>
       <c r="J218" s="15" t="n"/>
@@ -7865,17 +8379,17 @@
       <c r="N218" s="15" t="n"/>
     </row>
     <row r="219" ht="18" customHeight="1">
-      <c r="A219" s="14" t="inlineStr">
-        <is>
-          <t>3er lugar</t>
-        </is>
-      </c>
-      <c r="B219" s="15" t="n"/>
-      <c r="C219" s="15" t="n"/>
-      <c r="D219" s="15" t="n"/>
-      <c r="E219" s="15" t="n"/>
-      <c r="F219" s="15" t="n"/>
-      <c r="G219" s="15" t="n"/>
+      <c r="A219" s="285" t="inlineStr">
+        <is>
+          <t>3er</t>
+        </is>
+      </c>
+      <c r="B219" s="286" t="n"/>
+      <c r="C219" s="287" t="n"/>
+      <c r="D219" s="287" t="n"/>
+      <c r="E219" s="287" t="n"/>
+      <c r="F219" s="287" t="n"/>
+      <c r="G219" s="287" t="n"/>
       <c r="H219" s="15" t="n"/>
       <c r="I219" s="15" t="n"/>
       <c r="J219" s="15" t="n"/>
@@ -7885,17 +8399,17 @@
       <c r="N219" s="15" t="n"/>
     </row>
     <row r="220" ht="18" customHeight="1">
-      <c r="A220" s="14" t="inlineStr">
-        <is>
-          <t>4o lugar</t>
-        </is>
-      </c>
-      <c r="B220" s="15" t="n"/>
-      <c r="C220" s="15" t="n"/>
-      <c r="D220" s="15" t="n"/>
-      <c r="E220" s="15" t="n"/>
-      <c r="F220" s="15" t="n"/>
-      <c r="G220" s="15" t="n"/>
+      <c r="A220" s="285" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="B220" s="286" t="n"/>
+      <c r="C220" s="287" t="n"/>
+      <c r="D220" s="287" t="n"/>
+      <c r="E220" s="287" t="n"/>
+      <c r="F220" s="287" t="n"/>
+      <c r="G220" s="287" t="n"/>
       <c r="H220" s="15" t="n"/>
       <c r="I220" s="15" t="n"/>
       <c r="J220" s="15" t="n"/>
@@ -7905,17 +8419,17 @@
       <c r="N220" s="15" t="n"/>
     </row>
     <row r="221" ht="18" customHeight="1">
-      <c r="A221" s="14" t="inlineStr">
-        <is>
-          <t>5o lugar</t>
-        </is>
-      </c>
-      <c r="B221" s="15" t="n"/>
-      <c r="C221" s="15" t="n"/>
-      <c r="D221" s="15" t="n"/>
-      <c r="E221" s="15" t="n"/>
-      <c r="F221" s="15" t="n"/>
-      <c r="G221" s="15" t="n"/>
+      <c r="A221" s="285" t="inlineStr">
+        <is>
+          <t>5o</t>
+        </is>
+      </c>
+      <c r="B221" s="286" t="n"/>
+      <c r="C221" s="287" t="n"/>
+      <c r="D221" s="287" t="n"/>
+      <c r="E221" s="287" t="n"/>
+      <c r="F221" s="287" t="n"/>
+      <c r="G221" s="287" t="n"/>
       <c r="H221" s="15" t="n"/>
       <c r="I221" s="15" t="n"/>
       <c r="J221" s="15" t="n"/>
@@ -7924,9 +8438,9 @@
       <c r="M221" s="15" t="n"/>
       <c r="N221" s="15" t="n"/>
     </row>
-    <row r="222" ht="6" customHeight="1"/>
-    <row r="223">
-      <c r="A223" s="82" t="inlineStr">
+    <row r="222" ht="18" customHeight="1"/>
+    <row r="223" ht="18" customHeight="1">
+      <c r="A223" s="280" t="inlineStr">
         <is>
           <t>PROYECCIÓN MARZO → MARZO</t>
         </is>
@@ -7945,91 +8459,94 @@
       <c r="M223" s="28" t="n"/>
       <c r="N223" s="28" t="n"/>
     </row>
-    <row r="224">
-      <c r="A224" s="19" t="inlineStr">
+    <row r="224" ht="18" customHeight="1">
+      <c r="A224" s="281" t="inlineStr">
         <is>
           <t>Proyección MARZO</t>
         </is>
       </c>
-      <c r="B224" s="20" t="n"/>
-    </row>
-    <row r="226" ht="14" customHeight="1"/>
-    <row r="227" ht="22" customHeight="1">
-      <c r="A227" s="4" t="inlineStr">
+      <c r="B224" s="282" t="n">
+        <v>996614</v>
+      </c>
+    </row>
+    <row r="225" ht="18" customHeight="1"/>
+    <row r="226" ht="18" customHeight="1"/>
+    <row r="227" ht="24" customHeight="1">
+      <c r="A227" s="277" t="inlineStr">
         <is>
           <t>ABRIL 2026</t>
         </is>
       </c>
     </row>
-    <row r="228" ht="28" customHeight="1">
-      <c r="A228" s="5" t="inlineStr">
+    <row r="228" ht="18" customHeight="1">
+      <c r="A228" s="278" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
         </is>
       </c>
-      <c r="B228" s="5" t="inlineStr">
+      <c r="B228" s="288" t="inlineStr">
         <is>
           <t>TOTAL ($)</t>
         </is>
       </c>
-      <c r="C228" s="5" t="inlineStr">
+      <c r="C228" s="288" t="inlineStr">
         <is>
           <t>TOP 1</t>
         </is>
       </c>
-      <c r="D228" s="5" t="inlineStr">
+      <c r="D228" s="288" t="inlineStr">
         <is>
           <t>TOP 2</t>
         </is>
       </c>
-      <c r="E228" s="5" t="inlineStr">
+      <c r="E228" s="288" t="inlineStr">
         <is>
           <t>TOP 3</t>
         </is>
       </c>
-      <c r="F228" s="5" t="inlineStr">
+      <c r="F228" s="288" t="inlineStr">
         <is>
           <t>TOP 4</t>
         </is>
       </c>
-      <c r="G228" s="5" t="inlineStr">
+      <c r="G228" s="288" t="inlineStr">
         <is>
           <t>TOP 5</t>
         </is>
       </c>
-      <c r="H228" s="5" t="inlineStr">
+      <c r="H228" s="288" t="inlineStr">
         <is>
           <t>% TOP 1</t>
         </is>
       </c>
-      <c r="I228" s="5" t="inlineStr">
+      <c r="I228" s="288" t="inlineStr">
         <is>
           <t>% TOP 2</t>
         </is>
       </c>
-      <c r="J228" s="5" t="inlineStr">
+      <c r="J228" s="288" t="inlineStr">
         <is>
           <t>% TOP 3</t>
         </is>
       </c>
-      <c r="K228" s="5" t="inlineStr">
+      <c r="K228" s="288" t="inlineStr">
         <is>
           <t>% TOP 4</t>
         </is>
       </c>
-      <c r="L228" s="5" t="inlineStr">
+      <c r="L228" s="288" t="inlineStr">
         <is>
           <t>% TOP 5</t>
         </is>
       </c>
-      <c r="M228" s="5" t="inlineStr">
+      <c r="M228" s="288" t="inlineStr">
         <is>
           <t>% ACUM.</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="35" t="inlineStr">
+    <row r="229" ht="18" customHeight="1">
+      <c r="A229" s="279" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
@@ -8048,8 +8565,8 @@
       <c r="M229" s="28" t="n"/>
       <c r="N229" s="28" t="n"/>
     </row>
-    <row r="230">
-      <c r="A230" s="8" t="inlineStr">
+    <row r="230" ht="18" customHeight="1">
+      <c r="A230" s="278" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
@@ -8070,8 +8587,8 @@
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="8" t="inlineStr">
+    <row r="231" ht="18" customHeight="1">
+      <c r="A231" s="278" t="inlineStr">
         <is>
           <t>Fecha de corte</t>
         </is>
@@ -8084,8 +8601,8 @@
       </c>
       <c r="F231" s="10" t="n"/>
     </row>
-    <row r="232">
-      <c r="A232" s="8" t="inlineStr">
+    <row r="232" ht="18" customHeight="1">
+      <c r="A232" s="278" t="inlineStr">
         <is>
           <t>Reportado por</t>
         </is>
@@ -8098,9 +8615,9 @@
       </c>
       <c r="F232" s="10" t="n"/>
     </row>
-    <row r="233" ht="6" customHeight="1"/>
-    <row r="234">
-      <c r="A234" s="35" t="inlineStr">
+    <row r="233" ht="18" customHeight="1"/>
+    <row r="234" ht="18" customHeight="1">
+      <c r="A234" s="280" t="inlineStr">
         <is>
           <t>COBRANZA CORRIENTE</t>
         </is>
@@ -8119,25 +8636,27 @@
       <c r="M234" s="28" t="n"/>
       <c r="N234" s="28" t="n"/>
     </row>
-    <row r="235" ht="20" customHeight="1">
-      <c r="A235" s="8" t="inlineStr">
+    <row r="235" ht="18" customHeight="1">
+      <c r="A235" s="281" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B235" s="11" t="n"/>
+      <c r="B235" s="282" t="n">
+        <v>1333269</v>
+      </c>
     </row>
     <row r="236" ht="18" customHeight="1">
-      <c r="A236" s="12" t="inlineStr">
+      <c r="A236" s="283" t="inlineStr">
         <is>
           <t>Top 5</t>
         </is>
       </c>
-      <c r="C236" s="13" t="n"/>
-      <c r="D236" s="13" t="n"/>
-      <c r="E236" s="13" t="n"/>
-      <c r="F236" s="13" t="n"/>
-      <c r="G236" s="13" t="n"/>
+      <c r="C236" s="284" t="n"/>
+      <c r="D236" s="284" t="n"/>
+      <c r="E236" s="284" t="n"/>
+      <c r="F236" s="284" t="n"/>
+      <c r="G236" s="284" t="n"/>
       <c r="H236" s="13" t="n"/>
       <c r="I236" s="13" t="n"/>
       <c r="J236" s="13" t="n"/>
@@ -8147,17 +8666,23 @@
       <c r="N236" s="13" t="n"/>
     </row>
     <row r="237" ht="18" customHeight="1">
-      <c r="A237" s="14" t="inlineStr">
-        <is>
-          <t>1er lugar</t>
-        </is>
-      </c>
-      <c r="B237" s="15" t="n"/>
-      <c r="C237" s="15" t="n"/>
-      <c r="D237" s="15" t="n"/>
-      <c r="E237" s="15" t="n"/>
-      <c r="F237" s="15" t="n"/>
-      <c r="G237" s="15" t="n"/>
+      <c r="A237" s="285" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="B237" s="286" t="n">
+        <v>252756</v>
+      </c>
+      <c r="C237" s="287" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="D237" s="287" t="n"/>
+      <c r="E237" s="287" t="n"/>
+      <c r="F237" s="287" t="n"/>
+      <c r="G237" s="287" t="n"/>
       <c r="H237" s="15" t="n"/>
       <c r="I237" s="15" t="n"/>
       <c r="J237" s="15" t="n"/>
@@ -8167,17 +8692,23 @@
       <c r="N237" s="15" t="n"/>
     </row>
     <row r="238" ht="18" customHeight="1">
-      <c r="A238" s="14" t="inlineStr">
-        <is>
-          <t>2o lugar</t>
-        </is>
-      </c>
-      <c r="B238" s="15" t="n"/>
-      <c r="C238" s="15" t="n"/>
-      <c r="D238" s="15" t="n"/>
-      <c r="E238" s="15" t="n"/>
-      <c r="F238" s="15" t="n"/>
-      <c r="G238" s="15" t="n"/>
+      <c r="A238" s="285" t="inlineStr">
+        <is>
+          <t>2o</t>
+        </is>
+      </c>
+      <c r="B238" s="286" t="n">
+        <v>232738</v>
+      </c>
+      <c r="C238" s="287" t="n"/>
+      <c r="D238" s="287" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="E238" s="287" t="n"/>
+      <c r="F238" s="287" t="n"/>
+      <c r="G238" s="287" t="n"/>
       <c r="H238" s="15" t="n"/>
       <c r="I238" s="15" t="n"/>
       <c r="J238" s="15" t="n"/>
@@ -8187,17 +8718,23 @@
       <c r="N238" s="15" t="n"/>
     </row>
     <row r="239" ht="18" customHeight="1">
-      <c r="A239" s="14" t="inlineStr">
-        <is>
-          <t>3er lugar</t>
-        </is>
-      </c>
-      <c r="B239" s="15" t="n"/>
-      <c r="C239" s="15" t="n"/>
-      <c r="D239" s="15" t="n"/>
-      <c r="E239" s="15" t="n"/>
-      <c r="F239" s="15" t="n"/>
-      <c r="G239" s="15" t="n"/>
+      <c r="A239" s="285" t="inlineStr">
+        <is>
+          <t>3er</t>
+        </is>
+      </c>
+      <c r="B239" s="286" t="n">
+        <v>189665</v>
+      </c>
+      <c r="C239" s="287" t="n"/>
+      <c r="D239" s="287" t="n"/>
+      <c r="E239" s="287" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="F239" s="287" t="n"/>
+      <c r="G239" s="287" t="n"/>
       <c r="H239" s="15" t="n"/>
       <c r="I239" s="15" t="n"/>
       <c r="J239" s="15" t="n"/>
@@ -8207,17 +8744,23 @@
       <c r="N239" s="15" t="n"/>
     </row>
     <row r="240" ht="18" customHeight="1">
-      <c r="A240" s="14" t="inlineStr">
-        <is>
-          <t>4o lugar</t>
-        </is>
-      </c>
-      <c r="B240" s="15" t="n"/>
-      <c r="C240" s="15" t="n"/>
-      <c r="D240" s="15" t="n"/>
-      <c r="E240" s="15" t="n"/>
-      <c r="F240" s="15" t="n"/>
-      <c r="G240" s="15" t="n"/>
+      <c r="A240" s="285" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="B240" s="286" t="n">
+        <v>176792</v>
+      </c>
+      <c r="C240" s="287" t="n"/>
+      <c r="D240" s="287" t="n"/>
+      <c r="E240" s="287" t="n"/>
+      <c r="F240" s="287" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
+      <c r="G240" s="287" t="n"/>
       <c r="H240" s="15" t="n"/>
       <c r="I240" s="15" t="n"/>
       <c r="J240" s="15" t="n"/>
@@ -8227,17 +8770,23 @@
       <c r="N240" s="15" t="n"/>
     </row>
     <row r="241" ht="18" customHeight="1">
-      <c r="A241" s="14" t="inlineStr">
-        <is>
-          <t>5o lugar</t>
-        </is>
-      </c>
-      <c r="B241" s="15" t="n"/>
-      <c r="C241" s="15" t="n"/>
-      <c r="D241" s="15" t="n"/>
-      <c r="E241" s="15" t="n"/>
-      <c r="F241" s="15" t="n"/>
-      <c r="G241" s="15" t="n"/>
+      <c r="A241" s="285" t="inlineStr">
+        <is>
+          <t>5o</t>
+        </is>
+      </c>
+      <c r="B241" s="286" t="n">
+        <v>104567</v>
+      </c>
+      <c r="C241" s="287" t="n"/>
+      <c r="D241" s="287" t="n"/>
+      <c r="E241" s="287" t="n"/>
+      <c r="F241" s="287" t="n"/>
+      <c r="G241" s="287" t="inlineStr">
+        <is>
+          <t>V56</t>
+        </is>
+      </c>
       <c r="H241" s="15" t="n"/>
       <c r="I241" s="15" t="n"/>
       <c r="J241" s="15" t="n"/>
@@ -8246,9 +8795,9 @@
       <c r="M241" s="15" t="n"/>
       <c r="N241" s="15" t="n"/>
     </row>
-    <row r="242" ht="6" customHeight="1"/>
-    <row r="243">
-      <c r="A243" s="35" t="inlineStr">
+    <row r="242" ht="18" customHeight="1"/>
+    <row r="243" ht="18" customHeight="1">
+      <c r="A243" s="280" t="inlineStr">
         <is>
           <t>CANCELACIONES</t>
         </is>
@@ -8267,25 +8816,27 @@
       <c r="M243" s="28" t="n"/>
       <c r="N243" s="28" t="n"/>
     </row>
-    <row r="244" ht="20" customHeight="1">
-      <c r="A244" s="16" t="inlineStr">
+    <row r="244" ht="18" customHeight="1">
+      <c r="A244" s="281" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B244" s="17" t="n"/>
+      <c r="B244" s="282" t="n">
+        <v>116313</v>
+      </c>
     </row>
     <row r="245" ht="18" customHeight="1">
-      <c r="A245" s="12" t="inlineStr">
+      <c r="A245" s="283" t="inlineStr">
         <is>
           <t>Top 5</t>
         </is>
       </c>
-      <c r="C245" s="13" t="n"/>
-      <c r="D245" s="13" t="n"/>
-      <c r="E245" s="13" t="n"/>
-      <c r="F245" s="13" t="n"/>
-      <c r="G245" s="13" t="n"/>
+      <c r="C245" s="284" t="n"/>
+      <c r="D245" s="284" t="n"/>
+      <c r="E245" s="284" t="n"/>
+      <c r="F245" s="284" t="n"/>
+      <c r="G245" s="284" t="n"/>
       <c r="H245" s="13" t="n"/>
       <c r="I245" s="13" t="n"/>
       <c r="J245" s="13" t="n"/>
@@ -8295,17 +8846,23 @@
       <c r="N245" s="13" t="n"/>
     </row>
     <row r="246" ht="18" customHeight="1">
-      <c r="A246" s="14" t="inlineStr">
-        <is>
-          <t>1er lugar</t>
-        </is>
-      </c>
-      <c r="B246" s="15" t="n"/>
-      <c r="C246" s="15" t="n"/>
-      <c r="D246" s="15" t="n"/>
-      <c r="E246" s="15" t="n"/>
-      <c r="F246" s="15" t="n"/>
-      <c r="G246" s="15" t="n"/>
+      <c r="A246" s="285" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="B246" s="286" t="n">
+        <v>16519</v>
+      </c>
+      <c r="C246" s="287" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="D246" s="287" t="n"/>
+      <c r="E246" s="287" t="n"/>
+      <c r="F246" s="287" t="n"/>
+      <c r="G246" s="287" t="n"/>
       <c r="H246" s="15" t="n"/>
       <c r="I246" s="15" t="n"/>
       <c r="J246" s="15" t="n"/>
@@ -8315,17 +8872,23 @@
       <c r="N246" s="15" t="n"/>
     </row>
     <row r="247" ht="18" customHeight="1">
-      <c r="A247" s="14" t="inlineStr">
-        <is>
-          <t>2o lugar</t>
-        </is>
-      </c>
-      <c r="B247" s="15" t="n"/>
-      <c r="C247" s="15" t="n"/>
-      <c r="D247" s="15" t="n"/>
-      <c r="E247" s="15" t="n"/>
-      <c r="F247" s="15" t="n"/>
-      <c r="G247" s="15" t="n"/>
+      <c r="A247" s="285" t="inlineStr">
+        <is>
+          <t>2o</t>
+        </is>
+      </c>
+      <c r="B247" s="286" t="n">
+        <v>16242</v>
+      </c>
+      <c r="C247" s="287" t="n"/>
+      <c r="D247" s="287" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
+      <c r="E247" s="287" t="n"/>
+      <c r="F247" s="287" t="n"/>
+      <c r="G247" s="287" t="n"/>
       <c r="H247" s="15" t="n"/>
       <c r="I247" s="15" t="n"/>
       <c r="J247" s="15" t="n"/>
@@ -8335,17 +8898,23 @@
       <c r="N247" s="15" t="n"/>
     </row>
     <row r="248" ht="18" customHeight="1">
-      <c r="A248" s="14" t="inlineStr">
-        <is>
-          <t>3er lugar</t>
-        </is>
-      </c>
-      <c r="B248" s="15" t="n"/>
-      <c r="C248" s="15" t="n"/>
-      <c r="D248" s="15" t="n"/>
-      <c r="E248" s="15" t="n"/>
-      <c r="F248" s="15" t="n"/>
-      <c r="G248" s="15" t="n"/>
+      <c r="A248" s="285" t="inlineStr">
+        <is>
+          <t>3er</t>
+        </is>
+      </c>
+      <c r="B248" s="286" t="n">
+        <v>15691</v>
+      </c>
+      <c r="C248" s="287" t="n"/>
+      <c r="D248" s="287" t="n"/>
+      <c r="E248" s="287" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="F248" s="287" t="n"/>
+      <c r="G248" s="287" t="n"/>
       <c r="H248" s="15" t="n"/>
       <c r="I248" s="15" t="n"/>
       <c r="J248" s="15" t="n"/>
@@ -8355,17 +8924,23 @@
       <c r="N248" s="15" t="n"/>
     </row>
     <row r="249" ht="18" customHeight="1">
-      <c r="A249" s="14" t="inlineStr">
-        <is>
-          <t>4o lugar</t>
-        </is>
-      </c>
-      <c r="B249" s="15" t="n"/>
-      <c r="C249" s="15" t="n"/>
-      <c r="D249" s="15" t="n"/>
-      <c r="E249" s="15" t="n"/>
-      <c r="F249" s="15" t="n"/>
-      <c r="G249" s="15" t="n"/>
+      <c r="A249" s="285" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="B249" s="286" t="n">
+        <v>13754</v>
+      </c>
+      <c r="C249" s="287" t="n"/>
+      <c r="D249" s="287" t="n"/>
+      <c r="E249" s="287" t="n"/>
+      <c r="F249" s="287" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="G249" s="287" t="n"/>
       <c r="H249" s="15" t="n"/>
       <c r="I249" s="15" t="n"/>
       <c r="J249" s="15" t="n"/>
@@ -8375,17 +8950,23 @@
       <c r="N249" s="15" t="n"/>
     </row>
     <row r="250" ht="18" customHeight="1">
-      <c r="A250" s="14" t="inlineStr">
-        <is>
-          <t>5o lugar</t>
-        </is>
-      </c>
-      <c r="B250" s="15" t="n"/>
-      <c r="C250" s="15" t="n"/>
-      <c r="D250" s="15" t="n"/>
-      <c r="E250" s="15" t="n"/>
-      <c r="F250" s="15" t="n"/>
-      <c r="G250" s="15" t="n"/>
+      <c r="A250" s="285" t="inlineStr">
+        <is>
+          <t>5o</t>
+        </is>
+      </c>
+      <c r="B250" s="286" t="n">
+        <v>13047</v>
+      </c>
+      <c r="C250" s="287" t="n"/>
+      <c r="D250" s="287" t="n"/>
+      <c r="E250" s="287" t="n"/>
+      <c r="F250" s="287" t="n"/>
+      <c r="G250" s="287" t="inlineStr">
+        <is>
+          <t>V56</t>
+        </is>
+      </c>
       <c r="H250" s="15" t="n"/>
       <c r="I250" s="15" t="n"/>
       <c r="J250" s="15" t="n"/>
@@ -8394,9 +8975,9 @@
       <c r="M250" s="15" t="n"/>
       <c r="N250" s="15" t="n"/>
     </row>
-    <row r="251" ht="6" customHeight="1"/>
-    <row r="252">
-      <c r="A252" s="35" t="inlineStr">
+    <row r="251" ht="18" customHeight="1"/>
+    <row r="252" ht="18" customHeight="1">
+      <c r="A252" s="280" t="inlineStr">
         <is>
           <t>COBRANZA VENCIDA</t>
         </is>
@@ -8415,25 +8996,27 @@
       <c r="M252" s="28" t="n"/>
       <c r="N252" s="28" t="n"/>
     </row>
-    <row r="253" ht="20" customHeight="1">
-      <c r="A253" s="8" t="inlineStr">
+    <row r="253" ht="18" customHeight="1">
+      <c r="A253" s="281" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B253" s="11" t="n"/>
+      <c r="B253" s="282" t="n">
+        <v>142779</v>
+      </c>
     </row>
     <row r="254" ht="18" customHeight="1">
-      <c r="A254" s="12" t="inlineStr">
+      <c r="A254" s="283" t="inlineStr">
         <is>
           <t>Top 5</t>
         </is>
       </c>
-      <c r="C254" s="13" t="n"/>
-      <c r="D254" s="13" t="n"/>
-      <c r="E254" s="13" t="n"/>
-      <c r="F254" s="13" t="n"/>
-      <c r="G254" s="13" t="n"/>
+      <c r="C254" s="284" t="n"/>
+      <c r="D254" s="284" t="n"/>
+      <c r="E254" s="284" t="n"/>
+      <c r="F254" s="284" t="n"/>
+      <c r="G254" s="284" t="n"/>
       <c r="H254" s="13" t="n"/>
       <c r="I254" s="13" t="n"/>
       <c r="J254" s="13" t="n"/>
@@ -8443,17 +9026,23 @@
       <c r="N254" s="13" t="n"/>
     </row>
     <row r="255" ht="18" customHeight="1">
-      <c r="A255" s="14" t="inlineStr">
-        <is>
-          <t>1er lugar</t>
-        </is>
-      </c>
-      <c r="B255" s="15" t="n"/>
-      <c r="C255" s="15" t="n"/>
-      <c r="D255" s="15" t="n"/>
-      <c r="E255" s="15" t="n"/>
-      <c r="F255" s="15" t="n"/>
-      <c r="G255" s="15" t="n"/>
+      <c r="A255" s="285" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="B255" s="286" t="n">
+        <v>22753</v>
+      </c>
+      <c r="C255" s="287" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="D255" s="287" t="n"/>
+      <c r="E255" s="287" t="n"/>
+      <c r="F255" s="287" t="n"/>
+      <c r="G255" s="287" t="n"/>
       <c r="H255" s="15" t="n"/>
       <c r="I255" s="15" t="n"/>
       <c r="J255" s="15" t="n"/>
@@ -8463,17 +9052,23 @@
       <c r="N255" s="15" t="n"/>
     </row>
     <row r="256" ht="18" customHeight="1">
-      <c r="A256" s="14" t="inlineStr">
-        <is>
-          <t>2o lugar</t>
-        </is>
-      </c>
-      <c r="B256" s="15" t="n"/>
-      <c r="C256" s="15" t="n"/>
-      <c r="D256" s="15" t="n"/>
-      <c r="E256" s="15" t="n"/>
-      <c r="F256" s="15" t="n"/>
-      <c r="G256" s="15" t="n"/>
+      <c r="A256" s="285" t="inlineStr">
+        <is>
+          <t>2o</t>
+        </is>
+      </c>
+      <c r="B256" s="286" t="n">
+        <v>22418</v>
+      </c>
+      <c r="C256" s="287" t="n"/>
+      <c r="D256" s="287" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="E256" s="287" t="n"/>
+      <c r="F256" s="287" t="n"/>
+      <c r="G256" s="287" t="n"/>
       <c r="H256" s="15" t="n"/>
       <c r="I256" s="15" t="n"/>
       <c r="J256" s="15" t="n"/>
@@ -8483,17 +9078,23 @@
       <c r="N256" s="15" t="n"/>
     </row>
     <row r="257" ht="18" customHeight="1">
-      <c r="A257" s="14" t="inlineStr">
-        <is>
-          <t>3er lugar</t>
-        </is>
-      </c>
-      <c r="B257" s="15" t="n"/>
-      <c r="C257" s="15" t="n"/>
-      <c r="D257" s="15" t="n"/>
-      <c r="E257" s="15" t="n"/>
-      <c r="F257" s="15" t="n"/>
-      <c r="G257" s="15" t="n"/>
+      <c r="A257" s="285" t="inlineStr">
+        <is>
+          <t>3er</t>
+        </is>
+      </c>
+      <c r="B257" s="286" t="n">
+        <v>22157</v>
+      </c>
+      <c r="C257" s="287" t="n"/>
+      <c r="D257" s="287" t="n"/>
+      <c r="E257" s="287" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="F257" s="287" t="n"/>
+      <c r="G257" s="287" t="n"/>
       <c r="H257" s="15" t="n"/>
       <c r="I257" s="15" t="n"/>
       <c r="J257" s="15" t="n"/>
@@ -8503,17 +9104,23 @@
       <c r="N257" s="15" t="n"/>
     </row>
     <row r="258" ht="18" customHeight="1">
-      <c r="A258" s="14" t="inlineStr">
-        <is>
-          <t>4o lugar</t>
-        </is>
-      </c>
-      <c r="B258" s="15" t="n"/>
-      <c r="C258" s="15" t="n"/>
-      <c r="D258" s="15" t="n"/>
-      <c r="E258" s="15" t="n"/>
-      <c r="F258" s="15" t="n"/>
-      <c r="G258" s="15" t="n"/>
+      <c r="A258" s="285" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="B258" s="286" t="n">
+        <v>19559</v>
+      </c>
+      <c r="C258" s="287" t="n"/>
+      <c r="D258" s="287" t="n"/>
+      <c r="E258" s="287" t="n"/>
+      <c r="F258" s="287" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="G258" s="287" t="n"/>
       <c r="H258" s="15" t="n"/>
       <c r="I258" s="15" t="n"/>
       <c r="J258" s="15" t="n"/>
@@ -8523,17 +9130,23 @@
       <c r="N258" s="15" t="n"/>
     </row>
     <row r="259" ht="18" customHeight="1">
-      <c r="A259" s="14" t="inlineStr">
-        <is>
-          <t>5o lugar</t>
-        </is>
-      </c>
-      <c r="B259" s="15" t="n"/>
-      <c r="C259" s="15" t="n"/>
-      <c r="D259" s="15" t="n"/>
-      <c r="E259" s="15" t="n"/>
-      <c r="F259" s="15" t="n"/>
-      <c r="G259" s="15" t="n"/>
+      <c r="A259" s="285" t="inlineStr">
+        <is>
+          <t>5o</t>
+        </is>
+      </c>
+      <c r="B259" s="286" t="n">
+        <v>18767</v>
+      </c>
+      <c r="C259" s="287" t="n"/>
+      <c r="D259" s="287" t="n"/>
+      <c r="E259" s="287" t="n"/>
+      <c r="F259" s="287" t="n"/>
+      <c r="G259" s="287" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
       <c r="H259" s="15" t="n"/>
       <c r="I259" s="15" t="n"/>
       <c r="J259" s="15" t="n"/>
@@ -8542,9 +9155,9 @@
       <c r="M259" s="15" t="n"/>
       <c r="N259" s="15" t="n"/>
     </row>
-    <row r="260" ht="6" customHeight="1"/>
-    <row r="261">
-      <c r="A261" s="35" t="inlineStr">
+    <row r="260" ht="18" customHeight="1"/>
+    <row r="261" ht="18" customHeight="1">
+      <c r="A261" s="280" t="inlineStr">
         <is>
           <t>COBRANZA EFECTIVA</t>
         </is>
@@ -8563,25 +9176,27 @@
       <c r="M261" s="28" t="n"/>
       <c r="N261" s="28" t="n"/>
     </row>
-    <row r="262" ht="20" customHeight="1">
-      <c r="A262" s="16" t="inlineStr">
+    <row r="262" ht="18" customHeight="1">
+      <c r="A262" s="281" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B262" s="17" t="n"/>
+      <c r="B262" s="282" t="n">
+        <v>1017950</v>
+      </c>
     </row>
     <row r="263" ht="18" customHeight="1">
-      <c r="A263" s="12" t="inlineStr">
+      <c r="A263" s="283" t="inlineStr">
         <is>
           <t>Top 5</t>
         </is>
       </c>
-      <c r="C263" s="13" t="n"/>
-      <c r="D263" s="13" t="n"/>
-      <c r="E263" s="13" t="n"/>
-      <c r="F263" s="13" t="n"/>
-      <c r="G263" s="13" t="n"/>
+      <c r="C263" s="284" t="n"/>
+      <c r="D263" s="284" t="n"/>
+      <c r="E263" s="284" t="n"/>
+      <c r="F263" s="284" t="n"/>
+      <c r="G263" s="284" t="n"/>
       <c r="H263" s="13" t="n"/>
       <c r="I263" s="13" t="n"/>
       <c r="J263" s="13" t="n"/>
@@ -8591,17 +9206,23 @@
       <c r="N263" s="13" t="n"/>
     </row>
     <row r="264" ht="18" customHeight="1">
-      <c r="A264" s="14" t="inlineStr">
-        <is>
-          <t>1er lugar</t>
-        </is>
-      </c>
-      <c r="B264" s="15" t="n"/>
-      <c r="C264" s="15" t="n"/>
-      <c r="D264" s="15" t="n"/>
-      <c r="E264" s="15" t="n"/>
-      <c r="F264" s="15" t="n"/>
-      <c r="G264" s="15" t="n"/>
+      <c r="A264" s="285" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="B264" s="286" t="n">
+        <v>226674</v>
+      </c>
+      <c r="C264" s="287" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="D264" s="287" t="n"/>
+      <c r="E264" s="287" t="n"/>
+      <c r="F264" s="287" t="n"/>
+      <c r="G264" s="287" t="n"/>
       <c r="H264" s="15" t="n"/>
       <c r="I264" s="15" t="n"/>
       <c r="J264" s="15" t="n"/>
@@ -8611,17 +9232,23 @@
       <c r="N264" s="15" t="n"/>
     </row>
     <row r="265" ht="18" customHeight="1">
-      <c r="A265" s="14" t="inlineStr">
-        <is>
-          <t>2o lugar</t>
-        </is>
-      </c>
-      <c r="B265" s="15" t="n"/>
-      <c r="C265" s="15" t="n"/>
-      <c r="D265" s="15" t="n"/>
-      <c r="E265" s="15" t="n"/>
-      <c r="F265" s="15" t="n"/>
-      <c r="G265" s="15" t="n"/>
+      <c r="A265" s="285" t="inlineStr">
+        <is>
+          <t>2o</t>
+        </is>
+      </c>
+      <c r="B265" s="286" t="n">
+        <v>174488</v>
+      </c>
+      <c r="C265" s="287" t="n"/>
+      <c r="D265" s="287" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="E265" s="287" t="n"/>
+      <c r="F265" s="287" t="n"/>
+      <c r="G265" s="287" t="n"/>
       <c r="H265" s="15" t="n"/>
       <c r="I265" s="15" t="n"/>
       <c r="J265" s="15" t="n"/>
@@ -8631,17 +9258,23 @@
       <c r="N265" s="15" t="n"/>
     </row>
     <row r="266" ht="18" customHeight="1">
-      <c r="A266" s="14" t="inlineStr">
-        <is>
-          <t>3er lugar</t>
-        </is>
-      </c>
-      <c r="B266" s="15" t="n"/>
-      <c r="C266" s="15" t="n"/>
-      <c r="D266" s="15" t="n"/>
-      <c r="E266" s="15" t="n"/>
-      <c r="F266" s="15" t="n"/>
-      <c r="G266" s="15" t="n"/>
+      <c r="A266" s="285" t="inlineStr">
+        <is>
+          <t>3er</t>
+        </is>
+      </c>
+      <c r="B266" s="286" t="n">
+        <v>117049</v>
+      </c>
+      <c r="C266" s="287" t="n"/>
+      <c r="D266" s="287" t="n"/>
+      <c r="E266" s="287" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="F266" s="287" t="n"/>
+      <c r="G266" s="287" t="n"/>
       <c r="H266" s="15" t="n"/>
       <c r="I266" s="15" t="n"/>
       <c r="J266" s="15" t="n"/>
@@ -8651,17 +9284,23 @@
       <c r="N266" s="15" t="n"/>
     </row>
     <row r="267" ht="18" customHeight="1">
-      <c r="A267" s="14" t="inlineStr">
-        <is>
-          <t>4o lugar</t>
-        </is>
-      </c>
-      <c r="B267" s="15" t="n"/>
-      <c r="C267" s="15" t="n"/>
-      <c r="D267" s="15" t="n"/>
-      <c r="E267" s="15" t="n"/>
-      <c r="F267" s="15" t="n"/>
-      <c r="G267" s="15" t="n"/>
+      <c r="A267" s="285" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="B267" s="286" t="n">
+        <v>109425</v>
+      </c>
+      <c r="C267" s="287" t="n"/>
+      <c r="D267" s="287" t="n"/>
+      <c r="E267" s="287" t="n"/>
+      <c r="F267" s="287" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="G267" s="287" t="n"/>
       <c r="H267" s="15" t="n"/>
       <c r="I267" s="15" t="n"/>
       <c r="J267" s="15" t="n"/>
@@ -8671,17 +9310,23 @@
       <c r="N267" s="15" t="n"/>
     </row>
     <row r="268" ht="18" customHeight="1">
-      <c r="A268" s="14" t="inlineStr">
-        <is>
-          <t>5o lugar</t>
-        </is>
-      </c>
-      <c r="B268" s="15" t="n"/>
-      <c r="C268" s="15" t="n"/>
-      <c r="D268" s="15" t="n"/>
-      <c r="E268" s="15" t="n"/>
-      <c r="F268" s="15" t="n"/>
-      <c r="G268" s="15" t="n"/>
+      <c r="A268" s="285" t="inlineStr">
+        <is>
+          <t>5o</t>
+        </is>
+      </c>
+      <c r="B268" s="286" t="n">
+        <v>57711</v>
+      </c>
+      <c r="C268" s="287" t="n"/>
+      <c r="D268" s="287" t="n"/>
+      <c r="E268" s="287" t="n"/>
+      <c r="F268" s="287" t="n"/>
+      <c r="G268" s="287" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
       <c r="H268" s="15" t="n"/>
       <c r="I268" s="15" t="n"/>
       <c r="J268" s="15" t="n"/>
@@ -8690,9 +9335,9 @@
       <c r="M268" s="15" t="n"/>
       <c r="N268" s="15" t="n"/>
     </row>
-    <row r="269" ht="6" customHeight="1"/>
-    <row r="270">
-      <c r="A270" s="35" t="inlineStr">
+    <row r="269" ht="18" customHeight="1"/>
+    <row r="270" ht="18" customHeight="1">
+      <c r="A270" s="280" t="inlineStr">
         <is>
           <t>COBRANZA RECUPERADA</t>
         </is>
@@ -8711,25 +9356,27 @@
       <c r="M270" s="28" t="n"/>
       <c r="N270" s="28" t="n"/>
     </row>
-    <row r="271" ht="20" customHeight="1">
-      <c r="A271" s="8" t="inlineStr">
+    <row r="271" ht="18" customHeight="1">
+      <c r="A271" s="281" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B271" s="11" t="n"/>
+      <c r="B271" s="282" t="n">
+        <v>73871</v>
+      </c>
     </row>
     <row r="272" ht="18" customHeight="1">
-      <c r="A272" s="12" t="inlineStr">
+      <c r="A272" s="283" t="inlineStr">
         <is>
           <t>Top 5</t>
         </is>
       </c>
-      <c r="C272" s="13" t="n"/>
-      <c r="D272" s="13" t="n"/>
-      <c r="E272" s="13" t="n"/>
-      <c r="F272" s="13" t="n"/>
-      <c r="G272" s="13" t="n"/>
+      <c r="C272" s="284" t="n"/>
+      <c r="D272" s="284" t="n"/>
+      <c r="E272" s="284" t="n"/>
+      <c r="F272" s="284" t="n"/>
+      <c r="G272" s="284" t="n"/>
       <c r="H272" s="13" t="n"/>
       <c r="I272" s="13" t="n"/>
       <c r="J272" s="13" t="n"/>
@@ -8739,17 +9386,23 @@
       <c r="N272" s="13" t="n"/>
     </row>
     <row r="273" ht="18" customHeight="1">
-      <c r="A273" s="14" t="inlineStr">
-        <is>
-          <t>1er lugar</t>
-        </is>
-      </c>
-      <c r="B273" s="15" t="n"/>
-      <c r="C273" s="15" t="n"/>
-      <c r="D273" s="15" t="n"/>
-      <c r="E273" s="15" t="n"/>
-      <c r="F273" s="15" t="n"/>
-      <c r="G273" s="15" t="n"/>
+      <c r="A273" s="285" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="B273" s="286" t="n">
+        <v>30063</v>
+      </c>
+      <c r="C273" s="287" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="D273" s="287" t="n"/>
+      <c r="E273" s="287" t="n"/>
+      <c r="F273" s="287" t="n"/>
+      <c r="G273" s="287" t="n"/>
       <c r="H273" s="15" t="n"/>
       <c r="I273" s="15" t="n"/>
       <c r="J273" s="15" t="n"/>
@@ -8759,17 +9412,23 @@
       <c r="N273" s="15" t="n"/>
     </row>
     <row r="274" ht="18" customHeight="1">
-      <c r="A274" s="14" t="inlineStr">
-        <is>
-          <t>2o lugar</t>
-        </is>
-      </c>
-      <c r="B274" s="15" t="n"/>
-      <c r="C274" s="15" t="n"/>
-      <c r="D274" s="15" t="n"/>
-      <c r="E274" s="15" t="n"/>
-      <c r="F274" s="15" t="n"/>
-      <c r="G274" s="15" t="n"/>
+      <c r="A274" s="285" t="inlineStr">
+        <is>
+          <t>2o</t>
+        </is>
+      </c>
+      <c r="B274" s="286" t="n">
+        <v>10724</v>
+      </c>
+      <c r="C274" s="287" t="n"/>
+      <c r="D274" s="287" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="E274" s="287" t="n"/>
+      <c r="F274" s="287" t="n"/>
+      <c r="G274" s="287" t="n"/>
       <c r="H274" s="15" t="n"/>
       <c r="I274" s="15" t="n"/>
       <c r="J274" s="15" t="n"/>
@@ -8779,17 +9438,23 @@
       <c r="N274" s="15" t="n"/>
     </row>
     <row r="275" ht="18" customHeight="1">
-      <c r="A275" s="14" t="inlineStr">
-        <is>
-          <t>3er lugar</t>
-        </is>
-      </c>
-      <c r="B275" s="15" t="n"/>
-      <c r="C275" s="15" t="n"/>
-      <c r="D275" s="15" t="n"/>
-      <c r="E275" s="15" t="n"/>
-      <c r="F275" s="15" t="n"/>
-      <c r="G275" s="15" t="n"/>
+      <c r="A275" s="285" t="inlineStr">
+        <is>
+          <t>3er</t>
+        </is>
+      </c>
+      <c r="B275" s="286" t="n">
+        <v>9596</v>
+      </c>
+      <c r="C275" s="287" t="n"/>
+      <c r="D275" s="287" t="n"/>
+      <c r="E275" s="287" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="F275" s="287" t="n"/>
+      <c r="G275" s="287" t="n"/>
       <c r="H275" s="15" t="n"/>
       <c r="I275" s="15" t="n"/>
       <c r="J275" s="15" t="n"/>
@@ -8799,17 +9464,23 @@
       <c r="N275" s="15" t="n"/>
     </row>
     <row r="276" ht="18" customHeight="1">
-      <c r="A276" s="14" t="inlineStr">
-        <is>
-          <t>4o lugar</t>
-        </is>
-      </c>
-      <c r="B276" s="15" t="n"/>
-      <c r="C276" s="15" t="n"/>
-      <c r="D276" s="15" t="n"/>
-      <c r="E276" s="15" t="n"/>
-      <c r="F276" s="15" t="n"/>
-      <c r="G276" s="15" t="n"/>
+      <c r="A276" s="285" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="B276" s="286" t="n">
+        <v>7799</v>
+      </c>
+      <c r="C276" s="287" t="n"/>
+      <c r="D276" s="287" t="n"/>
+      <c r="E276" s="287" t="n"/>
+      <c r="F276" s="287" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="G276" s="287" t="n"/>
       <c r="H276" s="15" t="n"/>
       <c r="I276" s="15" t="n"/>
       <c r="J276" s="15" t="n"/>
@@ -8819,17 +9490,23 @@
       <c r="N276" s="15" t="n"/>
     </row>
     <row r="277" ht="18" customHeight="1">
-      <c r="A277" s="14" t="inlineStr">
-        <is>
-          <t>5o lugar</t>
-        </is>
-      </c>
-      <c r="B277" s="15" t="n"/>
-      <c r="C277" s="15" t="n"/>
-      <c r="D277" s="15" t="n"/>
-      <c r="E277" s="15" t="n"/>
-      <c r="F277" s="15" t="n"/>
-      <c r="G277" s="15" t="n"/>
+      <c r="A277" s="285" t="inlineStr">
+        <is>
+          <t>5o</t>
+        </is>
+      </c>
+      <c r="B277" s="286" t="n">
+        <v>5743</v>
+      </c>
+      <c r="C277" s="287" t="n"/>
+      <c r="D277" s="287" t="n"/>
+      <c r="E277" s="287" t="n"/>
+      <c r="F277" s="287" t="n"/>
+      <c r="G277" s="287" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
       <c r="H277" s="15" t="n"/>
       <c r="I277" s="15" t="n"/>
       <c r="J277" s="15" t="n"/>
@@ -8838,9 +9515,9 @@
       <c r="M277" s="15" t="n"/>
       <c r="N277" s="15" t="n"/>
     </row>
-    <row r="278" ht="6" customHeight="1"/>
-    <row r="279">
-      <c r="A279" s="35" t="inlineStr">
+    <row r="278" ht="18" customHeight="1"/>
+    <row r="279" ht="18" customHeight="1">
+      <c r="A279" s="280" t="inlineStr">
         <is>
           <t>COBRANZA TOTAL GENERAL</t>
         </is>
@@ -8859,25 +9536,27 @@
       <c r="M279" s="28" t="n"/>
       <c r="N279" s="28" t="n"/>
     </row>
-    <row r="280" ht="20" customHeight="1">
-      <c r="A280" s="16" t="inlineStr">
+    <row r="280" ht="18" customHeight="1">
+      <c r="A280" s="281" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B280" s="17" t="n"/>
+      <c r="B280" s="282" t="n">
+        <v>1136869</v>
+      </c>
     </row>
     <row r="281" ht="18" customHeight="1">
-      <c r="A281" s="12" t="inlineStr">
+      <c r="A281" s="283" t="inlineStr">
         <is>
           <t>Top 5</t>
         </is>
       </c>
-      <c r="C281" s="13" t="n"/>
-      <c r="D281" s="13" t="n"/>
-      <c r="E281" s="13" t="n"/>
-      <c r="F281" s="13" t="n"/>
-      <c r="G281" s="13" t="n"/>
+      <c r="C281" s="284" t="n"/>
+      <c r="D281" s="284" t="n"/>
+      <c r="E281" s="284" t="n"/>
+      <c r="F281" s="284" t="n"/>
+      <c r="G281" s="284" t="n"/>
       <c r="H281" s="13" t="n"/>
       <c r="I281" s="13" t="n"/>
       <c r="J281" s="13" t="n"/>
@@ -8887,17 +9566,23 @@
       <c r="N281" s="13" t="n"/>
     </row>
     <row r="282" ht="18" customHeight="1">
-      <c r="A282" s="14" t="inlineStr">
-        <is>
-          <t>1er lugar</t>
-        </is>
-      </c>
-      <c r="B282" s="15" t="n"/>
-      <c r="C282" s="15" t="n"/>
-      <c r="D282" s="15" t="n"/>
-      <c r="E282" s="15" t="n"/>
-      <c r="F282" s="15" t="n"/>
-      <c r="G282" s="15" t="n"/>
+      <c r="A282" s="285" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="B282" s="286" t="n">
+        <v>246701</v>
+      </c>
+      <c r="C282" s="287" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="D282" s="287" t="n"/>
+      <c r="E282" s="287" t="n"/>
+      <c r="F282" s="287" t="n"/>
+      <c r="G282" s="287" t="n"/>
       <c r="H282" s="15" t="n"/>
       <c r="I282" s="15" t="n"/>
       <c r="J282" s="15" t="n"/>
@@ -8907,17 +9592,23 @@
       <c r="N282" s="15" t="n"/>
     </row>
     <row r="283" ht="18" customHeight="1">
-      <c r="A283" s="14" t="inlineStr">
-        <is>
-          <t>2o lugar</t>
-        </is>
-      </c>
-      <c r="B283" s="15" t="n"/>
-      <c r="C283" s="15" t="n"/>
-      <c r="D283" s="15" t="n"/>
-      <c r="E283" s="15" t="n"/>
-      <c r="F283" s="15" t="n"/>
-      <c r="G283" s="15" t="n"/>
+      <c r="A283" s="285" t="inlineStr">
+        <is>
+          <t>2o</t>
+        </is>
+      </c>
+      <c r="B283" s="286" t="n">
+        <v>185092</v>
+      </c>
+      <c r="C283" s="287" t="n"/>
+      <c r="D283" s="287" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="E283" s="287" t="n"/>
+      <c r="F283" s="287" t="n"/>
+      <c r="G283" s="287" t="n"/>
       <c r="H283" s="15" t="n"/>
       <c r="I283" s="15" t="n"/>
       <c r="J283" s="15" t="n"/>
@@ -8927,17 +9618,23 @@
       <c r="N283" s="15" t="n"/>
     </row>
     <row r="284" ht="18" customHeight="1">
-      <c r="A284" s="14" t="inlineStr">
-        <is>
-          <t>3er lugar</t>
-        </is>
-      </c>
-      <c r="B284" s="15" t="n"/>
-      <c r="C284" s="15" t="n"/>
-      <c r="D284" s="15" t="n"/>
-      <c r="E284" s="15" t="n"/>
-      <c r="F284" s="15" t="n"/>
-      <c r="G284" s="15" t="n"/>
+      <c r="A284" s="285" t="inlineStr">
+        <is>
+          <t>3er</t>
+        </is>
+      </c>
+      <c r="B284" s="286" t="n">
+        <v>129392</v>
+      </c>
+      <c r="C284" s="287" t="n"/>
+      <c r="D284" s="287" t="n"/>
+      <c r="E284" s="287" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="F284" s="287" t="n"/>
+      <c r="G284" s="287" t="n"/>
       <c r="H284" s="15" t="n"/>
       <c r="I284" s="15" t="n"/>
       <c r="J284" s="15" t="n"/>
@@ -8947,17 +9644,23 @@
       <c r="N284" s="15" t="n"/>
     </row>
     <row r="285" ht="18" customHeight="1">
-      <c r="A285" s="14" t="inlineStr">
-        <is>
-          <t>4o lugar</t>
-        </is>
-      </c>
-      <c r="B285" s="15" t="n"/>
-      <c r="C285" s="15" t="n"/>
-      <c r="D285" s="15" t="n"/>
-      <c r="E285" s="15" t="n"/>
-      <c r="F285" s="15" t="n"/>
-      <c r="G285" s="15" t="n"/>
+      <c r="A285" s="285" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="B285" s="286" t="n">
+        <v>117118</v>
+      </c>
+      <c r="C285" s="287" t="n"/>
+      <c r="D285" s="287" t="n"/>
+      <c r="E285" s="287" t="n"/>
+      <c r="F285" s="287" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="G285" s="287" t="n"/>
       <c r="H285" s="15" t="n"/>
       <c r="I285" s="15" t="n"/>
       <c r="J285" s="15" t="n"/>
@@ -8967,17 +9670,23 @@
       <c r="N285" s="15" t="n"/>
     </row>
     <row r="286" ht="18" customHeight="1">
-      <c r="A286" s="14" t="inlineStr">
-        <is>
-          <t>5o lugar</t>
-        </is>
-      </c>
-      <c r="B286" s="15" t="n"/>
-      <c r="C286" s="15" t="n"/>
-      <c r="D286" s="15" t="n"/>
-      <c r="E286" s="15" t="n"/>
-      <c r="F286" s="15" t="n"/>
-      <c r="G286" s="15" t="n"/>
+      <c r="A286" s="285" t="inlineStr">
+        <is>
+          <t>5o</t>
+        </is>
+      </c>
+      <c r="B286" s="286" t="n">
+        <v>89557</v>
+      </c>
+      <c r="C286" s="287" t="n"/>
+      <c r="D286" s="287" t="n"/>
+      <c r="E286" s="287" t="n"/>
+      <c r="F286" s="287" t="n"/>
+      <c r="G286" s="287" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
       <c r="H286" s="15" t="n"/>
       <c r="I286" s="15" t="n"/>
       <c r="J286" s="15" t="n"/>
@@ -8986,9 +9695,9 @@
       <c r="M286" s="15" t="n"/>
       <c r="N286" s="15" t="n"/>
     </row>
-    <row r="287" ht="6" customHeight="1"/>
-    <row r="288">
-      <c r="A288" s="35" t="inlineStr">
+    <row r="287" ht="18" customHeight="1"/>
+    <row r="288" ht="18" customHeight="1">
+      <c r="A288" s="280" t="inlineStr">
         <is>
           <t>COBRANZA ADELANTADA F.</t>
         </is>
@@ -9007,25 +9716,27 @@
       <c r="M288" s="28" t="n"/>
       <c r="N288" s="28" t="n"/>
     </row>
-    <row r="289" ht="20" customHeight="1">
-      <c r="A289" s="8" t="inlineStr">
+    <row r="289" ht="18" customHeight="1">
+      <c r="A289" s="281" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B289" s="11" t="n"/>
+      <c r="B289" s="282" t="n">
+        <v>2689</v>
+      </c>
     </row>
     <row r="290" ht="18" customHeight="1">
-      <c r="A290" s="12" t="inlineStr">
+      <c r="A290" s="283" t="inlineStr">
         <is>
           <t>Top 5</t>
         </is>
       </c>
-      <c r="C290" s="13" t="n"/>
-      <c r="D290" s="13" t="n"/>
-      <c r="E290" s="13" t="n"/>
-      <c r="F290" s="13" t="n"/>
-      <c r="G290" s="13" t="n"/>
+      <c r="C290" s="284" t="n"/>
+      <c r="D290" s="284" t="n"/>
+      <c r="E290" s="284" t="n"/>
+      <c r="F290" s="284" t="n"/>
+      <c r="G290" s="284" t="n"/>
       <c r="H290" s="13" t="n"/>
       <c r="I290" s="13" t="n"/>
       <c r="J290" s="13" t="n"/>
@@ -9035,17 +9746,23 @@
       <c r="N290" s="13" t="n"/>
     </row>
     <row r="291" ht="18" customHeight="1">
-      <c r="A291" s="14" t="inlineStr">
-        <is>
-          <t>1er lugar</t>
-        </is>
-      </c>
-      <c r="B291" s="15" t="n"/>
-      <c r="C291" s="15" t="n"/>
-      <c r="D291" s="15" t="n"/>
-      <c r="E291" s="15" t="n"/>
-      <c r="F291" s="15" t="n"/>
-      <c r="G291" s="15" t="n"/>
+      <c r="A291" s="285" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="B291" s="286" t="n">
+        <v>2130</v>
+      </c>
+      <c r="C291" s="287" t="inlineStr">
+        <is>
+          <t>V55</t>
+        </is>
+      </c>
+      <c r="D291" s="287" t="n"/>
+      <c r="E291" s="287" t="n"/>
+      <c r="F291" s="287" t="n"/>
+      <c r="G291" s="287" t="n"/>
       <c r="H291" s="15" t="n"/>
       <c r="I291" s="15" t="n"/>
       <c r="J291" s="15" t="n"/>
@@ -9055,17 +9772,23 @@
       <c r="N291" s="15" t="n"/>
     </row>
     <row r="292" ht="18" customHeight="1">
-      <c r="A292" s="14" t="inlineStr">
-        <is>
-          <t>2o lugar</t>
-        </is>
-      </c>
-      <c r="B292" s="15" t="n"/>
-      <c r="C292" s="15" t="n"/>
-      <c r="D292" s="15" t="n"/>
-      <c r="E292" s="15" t="n"/>
-      <c r="F292" s="15" t="n"/>
-      <c r="G292" s="15" t="n"/>
+      <c r="A292" s="285" t="inlineStr">
+        <is>
+          <t>2o</t>
+        </is>
+      </c>
+      <c r="B292" s="286" t="n">
+        <v>559</v>
+      </c>
+      <c r="C292" s="287" t="n"/>
+      <c r="D292" s="287" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="E292" s="287" t="n"/>
+      <c r="F292" s="287" t="n"/>
+      <c r="G292" s="287" t="n"/>
       <c r="H292" s="15" t="n"/>
       <c r="I292" s="15" t="n"/>
       <c r="J292" s="15" t="n"/>
@@ -9075,17 +9798,17 @@
       <c r="N292" s="15" t="n"/>
     </row>
     <row r="293" ht="18" customHeight="1">
-      <c r="A293" s="14" t="inlineStr">
-        <is>
-          <t>3er lugar</t>
-        </is>
-      </c>
-      <c r="B293" s="15" t="n"/>
-      <c r="C293" s="15" t="n"/>
-      <c r="D293" s="15" t="n"/>
-      <c r="E293" s="15" t="n"/>
-      <c r="F293" s="15" t="n"/>
-      <c r="G293" s="15" t="n"/>
+      <c r="A293" s="285" t="inlineStr">
+        <is>
+          <t>3er</t>
+        </is>
+      </c>
+      <c r="B293" s="286" t="n"/>
+      <c r="C293" s="287" t="n"/>
+      <c r="D293" s="287" t="n"/>
+      <c r="E293" s="287" t="n"/>
+      <c r="F293" s="287" t="n"/>
+      <c r="G293" s="287" t="n"/>
       <c r="H293" s="15" t="n"/>
       <c r="I293" s="15" t="n"/>
       <c r="J293" s="15" t="n"/>
@@ -9095,17 +9818,17 @@
       <c r="N293" s="15" t="n"/>
     </row>
     <row r="294" ht="18" customHeight="1">
-      <c r="A294" s="14" t="inlineStr">
-        <is>
-          <t>4o lugar</t>
-        </is>
-      </c>
-      <c r="B294" s="15" t="n"/>
-      <c r="C294" s="15" t="n"/>
-      <c r="D294" s="15" t="n"/>
-      <c r="E294" s="15" t="n"/>
-      <c r="F294" s="15" t="n"/>
-      <c r="G294" s="15" t="n"/>
+      <c r="A294" s="285" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="B294" s="286" t="n"/>
+      <c r="C294" s="287" t="n"/>
+      <c r="D294" s="287" t="n"/>
+      <c r="E294" s="287" t="n"/>
+      <c r="F294" s="287" t="n"/>
+      <c r="G294" s="287" t="n"/>
       <c r="H294" s="15" t="n"/>
       <c r="I294" s="15" t="n"/>
       <c r="J294" s="15" t="n"/>
@@ -9115,17 +9838,17 @@
       <c r="N294" s="15" t="n"/>
     </row>
     <row r="295" ht="18" customHeight="1">
-      <c r="A295" s="14" t="inlineStr">
-        <is>
-          <t>5o lugar</t>
-        </is>
-      </c>
-      <c r="B295" s="15" t="n"/>
-      <c r="C295" s="15" t="n"/>
-      <c r="D295" s="15" t="n"/>
-      <c r="E295" s="15" t="n"/>
-      <c r="F295" s="15" t="n"/>
-      <c r="G295" s="15" t="n"/>
+      <c r="A295" s="285" t="inlineStr">
+        <is>
+          <t>5o</t>
+        </is>
+      </c>
+      <c r="B295" s="286" t="n"/>
+      <c r="C295" s="287" t="n"/>
+      <c r="D295" s="287" t="n"/>
+      <c r="E295" s="287" t="n"/>
+      <c r="F295" s="287" t="n"/>
+      <c r="G295" s="287" t="n"/>
       <c r="H295" s="15" t="n"/>
       <c r="I295" s="15" t="n"/>
       <c r="J295" s="15" t="n"/>
@@ -9134,9 +9857,9 @@
       <c r="M295" s="15" t="n"/>
       <c r="N295" s="15" t="n"/>
     </row>
-    <row r="296" ht="6" customHeight="1"/>
-    <row r="297">
-      <c r="A297" s="82" t="inlineStr">
+    <row r="296" ht="18" customHeight="1"/>
+    <row r="297" ht="18" customHeight="1">
+      <c r="A297" s="280" t="inlineStr">
         <is>
           <t>PROYECCIÓN ABRIL → ABRIL</t>
         </is>
@@ -9155,23 +9878,26 @@
       <c r="M297" s="28" t="n"/>
       <c r="N297" s="28" t="n"/>
     </row>
-    <row r="298">
-      <c r="A298" s="19" t="inlineStr">
+    <row r="298" ht="18" customHeight="1">
+      <c r="A298" s="281" t="inlineStr">
         <is>
           <t>Proyección ABRIL</t>
         </is>
       </c>
-      <c r="B298" s="20" t="n"/>
-    </row>
-    <row r="300" ht="14" customHeight="1"/>
-    <row r="301" ht="22" customHeight="1">
-      <c r="A301" s="4" t="inlineStr">
+      <c r="B298" s="282" t="n">
+        <v>1031832</v>
+      </c>
+    </row>
+    <row r="299" ht="18" customHeight="1"/>
+    <row r="300" ht="18" customHeight="1"/>
+    <row r="301" ht="24" customHeight="1">
+      <c r="A301" s="277" t="inlineStr">
         <is>
           <t>MAYO 2026</t>
         </is>
       </c>
     </row>
-    <row r="302" ht="28" customHeight="1">
+    <row r="302" ht="18" customHeight="1">
       <c r="A302" s="5" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
@@ -9238,7 +9964,7 @@
         </is>
       </c>
     </row>
-    <row r="303">
+    <row r="303" ht="18" customHeight="1">
       <c r="A303" s="35" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
@@ -9258,7 +9984,7 @@
       <c r="M303" s="28" t="n"/>
       <c r="N303" s="28" t="n"/>
     </row>
-    <row r="304">
+    <row r="304" ht="18" customHeight="1">
       <c r="A304" s="8" t="inlineStr">
         <is>
           <t>Mes</t>
@@ -9280,7 +10006,7 @@
         </is>
       </c>
     </row>
-    <row r="305">
+    <row r="305" ht="18" customHeight="1">
       <c r="A305" s="8" t="inlineStr">
         <is>
           <t>Fecha de corte</t>
@@ -9294,7 +10020,7 @@
       </c>
       <c r="F305" s="10" t="n"/>
     </row>
-    <row r="306">
+    <row r="306" ht="18" customHeight="1">
       <c r="A306" s="8" t="inlineStr">
         <is>
           <t>Reportado por</t>
@@ -9308,8 +10034,8 @@
       </c>
       <c r="F306" s="10" t="n"/>
     </row>
-    <row r="307" ht="6" customHeight="1"/>
-    <row r="308">
+    <row r="307" ht="18" customHeight="1"/>
+    <row r="308" ht="18" customHeight="1">
       <c r="A308" s="35" t="inlineStr">
         <is>
           <t>COBRANZA CORRIENTE</t>
@@ -9329,7 +10055,7 @@
       <c r="M308" s="28" t="n"/>
       <c r="N308" s="28" t="n"/>
     </row>
-    <row r="309" ht="20" customHeight="1">
+    <row r="309" ht="18" customHeight="1">
       <c r="A309" s="8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -9456,8 +10182,8 @@
       <c r="M315" s="15" t="n"/>
       <c r="N315" s="15" t="n"/>
     </row>
-    <row r="316" ht="6" customHeight="1"/>
-    <row r="317">
+    <row r="316" ht="18" customHeight="1"/>
+    <row r="317" ht="18" customHeight="1">
       <c r="A317" s="35" t="inlineStr">
         <is>
           <t>CANCELACIONES</t>
@@ -9477,7 +10203,7 @@
       <c r="M317" s="28" t="n"/>
       <c r="N317" s="28" t="n"/>
     </row>
-    <row r="318" ht="20" customHeight="1">
+    <row r="318" ht="18" customHeight="1">
       <c r="A318" s="16" t="inlineStr">
         <is>
           <t>Total</t>

--- a/workspaces/cobranza/estadisticas/ESTADISTICA_2026_CON_DROPDOWN.xlsx
+++ b/workspaces/cobranza/estadisticas/ESTADISTICA_2026_CON_DROPDOWN.xlsx
@@ -2778,25 +2778,25 @@
     </row>
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="297">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871)))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),58,132,206,280,354,428,502,576,650,724,798,872))</f>
         <v/>
       </c>
       <c r="B8" s="163" t="n"/>
       <c r="C8" s="164" t="n"/>
       <c r="D8" s="298">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),48,122,196,270,344,418,492,566,640,714,788,862)))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),49,123,197,271,345,419,493,567,641,715,789,863))</f>
         <v/>
       </c>
       <c r="E8" s="171" t="n"/>
       <c r="F8" s="172" t="n"/>
       <c r="G8" s="299">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),39,113,187,261,335,409,483,557,631,705,779,853)))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),40,114,188,262,336,410,484,558,632,706,780,854))</f>
         <v/>
       </c>
       <c r="H8" s="169" t="n"/>
       <c r="I8" s="170" t="n"/>
       <c r="J8" s="224">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),30,104,178,252,326,400,474,548,622,696,770,844)))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),20,96,170,244,318,392,466,540,614,688,762,836))</f>
         <v/>
       </c>
       <c r="K8" s="165" t="n"/>
@@ -2806,25 +2806,25 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="300">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),11,85,159,233,307,381,455,529,603,677,751,825)))/INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),20,96,170,244,318,392,466,540,614,688,762,836))/=INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),58,132,206,280,354,428,502,576,650,724,798,872))</f>
         <v/>
       </c>
       <c r="B9" s="45" t="n"/>
       <c r="C9" s="46" t="n"/>
       <c r="D9" s="301">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),48,122,196,270,344,418,492,566,640,714,788,862)))/INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),49,123,197,271,345,419,493,567,641,715,789,863))/=INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),58,132,206,280,354,428,502,576,650,724,798,872))</f>
         <v/>
       </c>
       <c r="E9" s="45" t="n"/>
       <c r="F9" s="46" t="n"/>
       <c r="G9" s="302">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),39,113,187,261,335,409,483,557,631,705,779,853)))/INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),40,114,188,262,336,410,484,558,632,706,780,854))/=INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),58,132,206,280,354,428,502,576,650,724,798,872))</f>
         <v/>
       </c>
       <c r="H9" s="45" t="n"/>
       <c r="I9" s="46" t="n"/>
       <c r="J9" s="267">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),30,104,178,252,326,400,474,548,622,696,770,844)))/INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),31,105,179,253,327,401,475,549,623,697,771,845))/=INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),58,132,206,280,354,428,502,576,650,724,798,872))</f>
         <v/>
       </c>
       <c r="K9" s="45" t="n"/>
@@ -2886,25 +2886,25 @@
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="305">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),11,85,159,233,307,381,455,529,603,677,751,825)))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),11,87,161,235,309,383,457,531,605,679,753,827))</f>
         <v/>
       </c>
       <c r="B12" s="163" t="n"/>
       <c r="C12" s="164" t="n"/>
       <c r="D12" s="306">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),35,109,183,257,331,405,479,553,627,701,775,849)))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),31,105,179,253,327,401,475,549,623,697,771,845))</f>
         <v/>
       </c>
       <c r="E12" s="167" t="n"/>
       <c r="F12" s="168" t="n"/>
       <c r="G12" s="307">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),66,140,214,288,362,436,510,584,658,732,806,880)))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),67,141,215,289,363,437,511,585,659,733,807,881))</f>
         <v/>
       </c>
       <c r="H12" s="173" t="n"/>
       <c r="I12" s="174" t="n"/>
       <c r="J12" s="234">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),76,150,224,298,372,446,520,594,668,742,816,890)))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),76,150,224,298,372,446,520,594,668,742,816,890))</f>
         <v/>
       </c>
       <c r="K12" s="175" t="n"/>
@@ -2913,27 +2913,26 @@
       <c r="N12" s="38" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="303" t="inlineStr">
-        <is>
-          <t>Total del mes</t>
-        </is>
+      <c r="A13" s="303">
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),11,87,161,235,309,383,457,531,605,679,753,827))/=INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),58,132,206,280,354,428,502,576,650,724,798,872))</f>
+        <v/>
       </c>
       <c r="B13" s="45" t="n"/>
       <c r="C13" s="46" t="n"/>
       <c r="D13" s="308">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),35,109,183,257,331,405,479,553,627,701,775,849)))/INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),31,105,179,253,327,401,475,549,623,697,771,845))/=INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),58,132,206,280,354,428,502,576,650,724,798,872))</f>
         <v/>
       </c>
       <c r="E13" s="45" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="309">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),66,140,214,288,362,436,510,584,658,732,806,880)))/INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),67,141,215,289,363,437,511,585,659,733,807,881))/=INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),58,132,206,280,354,428,502,576,650,724,798,872))</f>
         <v/>
       </c>
       <c r="H13" s="45" t="n"/>
       <c r="I13" s="46" t="n"/>
       <c r="J13" s="270">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),76,150,224,298,372,446,520,594,668,742,816,890)))/INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),76,150,224,298,372,446,520,594,668,742,816,890))/=INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),58,132,206,280,354,428,502,576,650,724,798,872))</f>
         <v/>
       </c>
       <c r="K13" s="45" t="n"/>
@@ -3032,7 +3031,7 @@
         </is>
       </c>
       <c r="B18" s="313">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),57,131,205,279,353,427,501,575,649,723,797,871)))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),58,132,206,280,354,428,502,576,650,724,798,872))</f>
         <v/>
       </c>
       <c r="C18" s="38" t="n"/>
@@ -3062,7 +3061,7 @@
         </is>
       </c>
       <c r="B19" s="317">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),48,122,196,270,344,418,492,566,640,714,788,862)))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),49,123,197,271,345,419,493,567,641,715,789,863))</f>
         <v/>
       </c>
       <c r="C19" s="38" t="n"/>
@@ -3092,7 +3091,7 @@
         </is>
       </c>
       <c r="B20" s="321">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),39,113,187,261,335,409,483,557,631,705,779,853)))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),40,114,188,262,336,410,484,558,632,706,780,854))</f>
         <v/>
       </c>
       <c r="C20" s="38" t="n"/>
@@ -3122,7 +3121,7 @@
         </is>
       </c>
       <c r="B21" s="325">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),30,104,178,252,326,400,474,548,622,696,770,844)))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),20,96,170,244,318,392,466,540,614,688,762,836))</f>
         <v/>
       </c>
       <c r="C21" s="38" t="n"/>
@@ -3152,7 +3151,7 @@
         </is>
       </c>
       <c r="B22" s="325">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,{"ENERO","FEBRERO","MARZO","ABRIL","MAYO","JUNIO","JULIO","AGOSTO","SEPTIEMBRE","OCTUBRE","NOVIEMBRE","DICIEMBRE"},0),35,109,183,257,331,405,479,553,627,701,775,849)))</f>
+        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),31,105,179,253,327,401,475,549,623,697,771,845))</f>
         <v/>
       </c>
       <c r="C22" s="38" t="n"/>
@@ -4426,7 +4425,11 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="240" t="n"/>
       <c r="B13" s="45" t="n"/>
-      <c r="C13" s="45" t="n"/>
+      <c r="C13" s="45" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
       <c r="D13" s="45" t="n"/>
       <c r="E13" s="45" t="n"/>
       <c r="F13" s="45" t="n"/>
@@ -4445,7 +4448,11 @@
       <c r="A14" s="241" t="n"/>
       <c r="B14" s="241" t="n"/>
       <c r="C14" s="242" t="n"/>
-      <c r="D14" s="241" t="n"/>
+      <c r="D14" s="241" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
       <c r="E14" s="242" t="n"/>
       <c r="F14" s="241" t="n"/>
       <c r="G14" s="242" t="n"/>
@@ -4464,7 +4471,11 @@
       <c r="B15" s="125" t="n"/>
       <c r="C15" s="242" t="n"/>
       <c r="D15" s="243" t="n"/>
-      <c r="E15" s="242" t="n"/>
+      <c r="E15" s="242" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
       <c r="F15" s="244" t="n"/>
       <c r="G15" s="242" t="n"/>
       <c r="H15" s="242" t="n"/>
@@ -4483,7 +4494,11 @@
       <c r="C16" s="242" t="n"/>
       <c r="D16" s="246" t="n"/>
       <c r="E16" s="242" t="n"/>
-      <c r="F16" s="247" t="n"/>
+      <c r="F16" s="247" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
       <c r="G16" s="242" t="n"/>
       <c r="H16" s="242" t="n"/>
       <c r="I16" s="242" t="n"/>
@@ -4502,7 +4517,11 @@
       <c r="D17" s="248" t="n"/>
       <c r="E17" s="242" t="n"/>
       <c r="F17" s="249" t="n"/>
-      <c r="G17" s="242" t="n"/>
+      <c r="G17" s="242" t="inlineStr">
+        <is>
+          <t>V27</t>
+        </is>
+      </c>
       <c r="H17" s="250" t="n"/>
       <c r="I17" s="242" t="n"/>
       <c r="J17" s="242" t="n"/>
@@ -4551,7 +4570,9 @@
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="255" t="n"/>
-      <c r="B20" s="256" t="n"/>
+      <c r="B20" s="256" t="n">
+        <v>127110</v>
+      </c>
       <c r="C20" s="257" t="n"/>
       <c r="D20" s="258" t="n"/>
       <c r="E20" s="257" t="n"/>
@@ -4596,7 +4617,7 @@
       <c r="B22" s="73" t="n"/>
       <c r="C22" s="74" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="D22" s="75" t="n">
@@ -4625,7 +4646,11 @@
       </c>
       <c r="B23" s="46" t="n"/>
       <c r="C23" s="48" t="n"/>
-      <c r="D23" s="48" t="n"/>
+      <c r="D23" s="48" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
       <c r="E23" s="78" t="inlineStr">
         <is>
           <t>V1</t>
@@ -4656,7 +4681,11 @@
       <c r="B24" s="48" t="n"/>
       <c r="C24" s="48" t="n"/>
       <c r="D24" s="62" t="n"/>
-      <c r="E24" s="48" t="n"/>
+      <c r="E24" s="48" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
       <c r="F24" s="48" t="n"/>
       <c r="G24" s="74" t="inlineStr">
         <is>
@@ -4687,7 +4716,11 @@
       <c r="C25" s="48" t="n"/>
       <c r="D25" s="48" t="n"/>
       <c r="E25" s="48" t="n"/>
-      <c r="F25" s="62" t="n"/>
+      <c r="F25" s="62" t="inlineStr">
+        <is>
+          <t>V56</t>
+        </is>
+      </c>
       <c r="G25" s="48" t="n"/>
       <c r="H25" s="48" t="n"/>
       <c r="I25" s="78" t="inlineStr">
@@ -4718,7 +4751,11 @@
       <c r="D26" s="48" t="n"/>
       <c r="E26" s="48" t="n"/>
       <c r="F26" s="48" t="n"/>
-      <c r="G26" s="48" t="n"/>
+      <c r="G26" s="48" t="inlineStr">
+        <is>
+          <t>V84</t>
+        </is>
+      </c>
       <c r="H26" s="62" t="n"/>
       <c r="I26" s="48" t="n"/>
       <c r="J26" s="48" t="n"/>
@@ -4868,7 +4905,11 @@
       </c>
       <c r="B34" s="15" t="n"/>
       <c r="C34" s="15" t="n"/>
-      <c r="D34" s="15" t="n"/>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
           <t>FRANCISCO</t>
@@ -4899,7 +4940,11 @@
       <c r="B35" s="15" t="n"/>
       <c r="C35" s="15" t="n"/>
       <c r="D35" s="15" t="n"/>
-      <c r="E35" s="15" t="n"/>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
       <c r="F35" s="15" t="n"/>
       <c r="G35" s="15" t="inlineStr">
         <is>
@@ -4930,7 +4975,11 @@
       <c r="C36" s="15" t="n"/>
       <c r="D36" s="15" t="n"/>
       <c r="E36" s="15" t="n"/>
-      <c r="F36" s="15" t="n"/>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
       <c r="G36" s="15" t="n"/>
       <c r="H36" s="15" t="n"/>
       <c r="I36" s="15" t="inlineStr">
@@ -4961,7 +5010,11 @@
       <c r="D37" s="15" t="n"/>
       <c r="E37" s="15" t="n"/>
       <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
       <c r="H37" s="15" t="n"/>
       <c r="I37" s="15" t="n"/>
       <c r="J37" s="15" t="n"/>
@@ -5068,7 +5121,11 @@
       </c>
       <c r="B43" s="15" t="n"/>
       <c r="C43" s="15" t="n"/>
-      <c r="D43" s="15" t="n"/>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
           <t>V6</t>
@@ -5099,7 +5156,11 @@
       <c r="B44" s="15" t="n"/>
       <c r="C44" s="15" t="n"/>
       <c r="D44" s="15" t="n"/>
-      <c r="E44" s="15" t="n"/>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
       <c r="F44" s="15" t="n"/>
       <c r="G44" s="15" t="inlineStr">
         <is>
@@ -5130,7 +5191,11 @@
       <c r="C45" s="15" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="15" t="n"/>
-      <c r="F45" s="15" t="n"/>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
       <c r="G45" s="15" t="n"/>
       <c r="H45" s="15" t="n"/>
       <c r="I45" s="15" t="inlineStr">
@@ -5161,7 +5226,11 @@
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="15" t="n"/>
       <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
       <c r="H46" s="15" t="n"/>
       <c r="I46" s="15" t="n"/>
       <c r="J46" s="15" t="n"/>
@@ -5239,7 +5308,7 @@
       <c r="B51" s="15" t="n"/>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>V39</t>
         </is>
       </c>
       <c r="D51" s="30" t="n">
@@ -5268,7 +5337,11 @@
       </c>
       <c r="B52" s="15" t="n"/>
       <c r="C52" s="15" t="n"/>
-      <c r="D52" s="15" t="n"/>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
           <t>V4</t>
@@ -5299,7 +5372,11 @@
       <c r="B53" s="15" t="n"/>
       <c r="C53" s="15" t="n"/>
       <c r="D53" s="15" t="n"/>
-      <c r="E53" s="15" t="n"/>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
       <c r="F53" s="15" t="n"/>
       <c r="G53" s="15" t="inlineStr">
         <is>
@@ -5330,7 +5407,11 @@
       <c r="C54" s="15" t="n"/>
       <c r="D54" s="15" t="n"/>
       <c r="E54" s="15" t="n"/>
-      <c r="F54" s="15" t="n"/>
+      <c r="F54" s="15" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
       <c r="G54" s="15" t="n"/>
       <c r="H54" s="15" t="n"/>
       <c r="I54" s="15" t="inlineStr">
@@ -5361,7 +5442,11 @@
       <c r="D55" s="15" t="n"/>
       <c r="E55" s="15" t="n"/>
       <c r="F55" s="15" t="n"/>
-      <c r="G55" s="15" t="n"/>
+      <c r="G55" s="15" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
       <c r="H55" s="15" t="n"/>
       <c r="I55" s="15" t="n"/>
       <c r="J55" s="15" t="n"/>
@@ -5468,7 +5553,11 @@
       </c>
       <c r="B61" s="15" t="n"/>
       <c r="C61" s="15" t="n"/>
-      <c r="D61" s="15" t="n"/>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
       <c r="E61" s="15" t="inlineStr">
         <is>
           <t>JORGE</t>
@@ -5499,7 +5588,11 @@
       <c r="B62" s="15" t="n"/>
       <c r="C62" s="15" t="n"/>
       <c r="D62" s="15" t="n"/>
-      <c r="E62" s="15" t="n"/>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
       <c r="F62" s="15" t="n"/>
       <c r="G62" s="15" t="inlineStr">
         <is>
@@ -5530,7 +5623,11 @@
       <c r="C63" s="15" t="n"/>
       <c r="D63" s="15" t="n"/>
       <c r="E63" s="15" t="n"/>
-      <c r="F63" s="15" t="n"/>
+      <c r="F63" s="15" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
       <c r="G63" s="15" t="n"/>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="15" t="inlineStr">
@@ -5561,7 +5658,11 @@
       <c r="D64" s="15" t="n"/>
       <c r="E64" s="15" t="n"/>
       <c r="F64" s="15" t="n"/>
-      <c r="G64" s="15" t="n"/>
+      <c r="G64" s="15" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="15" t="n"/>
       <c r="J64" s="15" t="n"/>
@@ -5974,7 +6075,9 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B87" s="11" t="n"/>
+      <c r="B87" s="11" t="n">
+        <v>1251614</v>
+      </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="12" t="inlineStr">
@@ -6001,8 +6104,14 @@
           <t>1er lugar</t>
         </is>
       </c>
-      <c r="B89" s="15" t="n"/>
-      <c r="C89" s="15" t="n"/>
+      <c r="B89" s="15" t="n">
+        <v>207793</v>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
       <c r="D89" s="15" t="n"/>
       <c r="E89" s="15" t="n"/>
       <c r="F89" s="15" t="n"/>
@@ -6021,9 +6130,15 @@
           <t>2o lugar</t>
         </is>
       </c>
-      <c r="B90" s="15" t="n"/>
+      <c r="B90" s="15" t="n">
+        <v>198234</v>
+      </c>
       <c r="C90" s="15" t="n"/>
-      <c r="D90" s="15" t="n"/>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
       <c r="E90" s="15" t="n"/>
       <c r="F90" s="15" t="n"/>
       <c r="G90" s="15" t="n"/>
@@ -6041,10 +6156,16 @@
           <t>3er lugar</t>
         </is>
       </c>
-      <c r="B91" s="15" t="n"/>
+      <c r="B91" s="15" t="n">
+        <v>156891</v>
+      </c>
       <c r="C91" s="15" t="n"/>
       <c r="D91" s="15" t="n"/>
-      <c r="E91" s="15" t="n"/>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
       <c r="F91" s="15" t="n"/>
       <c r="G91" s="15" t="n"/>
       <c r="H91" s="15" t="n"/>
@@ -6061,11 +6182,17 @@
           <t>4o lugar</t>
         </is>
       </c>
-      <c r="B92" s="15" t="n"/>
+      <c r="B92" s="15" t="n">
+        <v>142567</v>
+      </c>
       <c r="C92" s="15" t="n"/>
       <c r="D92" s="15" t="n"/>
       <c r="E92" s="15" t="n"/>
-      <c r="F92" s="15" t="n"/>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
       <c r="G92" s="15" t="n"/>
       <c r="H92" s="15" t="n"/>
       <c r="I92" s="15" t="n"/>
@@ -6081,12 +6208,18 @@
           <t>5o lugar</t>
         </is>
       </c>
-      <c r="B93" s="15" t="n"/>
+      <c r="B93" s="15" t="n">
+        <v>98765</v>
+      </c>
       <c r="C93" s="15" t="n"/>
       <c r="D93" s="15" t="n"/>
       <c r="E93" s="15" t="n"/>
       <c r="F93" s="15" t="n"/>
-      <c r="G93" s="15" t="n"/>
+      <c r="G93" s="15" t="inlineStr">
+        <is>
+          <t>V27</t>
+        </is>
+      </c>
       <c r="H93" s="15" t="n"/>
       <c r="I93" s="15" t="n"/>
       <c r="J93" s="15" t="n"/>
@@ -6122,7 +6255,9 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B96" s="17" t="n"/>
+      <c r="B96" s="17" t="n">
+        <v>127110</v>
+      </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="12" t="inlineStr">
@@ -6149,8 +6284,14 @@
           <t>1er lugar</t>
         </is>
       </c>
-      <c r="B98" s="15" t="n"/>
-      <c r="C98" s="15" t="n"/>
+      <c r="B98" s="15" t="n">
+        <v>21035</v>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>V38</t>
+        </is>
+      </c>
       <c r="D98" s="15" t="n"/>
       <c r="E98" s="15" t="n"/>
       <c r="F98" s="15" t="n"/>
@@ -6169,9 +6310,15 @@
           <t>2o lugar</t>
         </is>
       </c>
-      <c r="B99" s="15" t="n"/>
+      <c r="B99" s="15" t="n">
+        <v>17664</v>
+      </c>
       <c r="C99" s="15" t="n"/>
-      <c r="D99" s="15" t="n"/>
+      <c r="D99" s="15" t="inlineStr">
+        <is>
+          <t>V56</t>
+        </is>
+      </c>
       <c r="E99" s="15" t="n"/>
       <c r="F99" s="15" t="n"/>
       <c r="G99" s="15" t="n"/>
@@ -6189,10 +6336,16 @@
           <t>3er lugar</t>
         </is>
       </c>
-      <c r="B100" s="15" t="n"/>
+      <c r="B100" s="15" t="n">
+        <v>15924</v>
+      </c>
       <c r="C100" s="15" t="n"/>
       <c r="D100" s="15" t="n"/>
-      <c r="E100" s="15" t="n"/>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
       <c r="F100" s="15" t="n"/>
       <c r="G100" s="15" t="n"/>
       <c r="H100" s="15" t="n"/>
@@ -6209,11 +6362,17 @@
           <t>4o lugar</t>
         </is>
       </c>
-      <c r="B101" s="15" t="n"/>
+      <c r="B101" s="15" t="n">
+        <v>14374</v>
+      </c>
       <c r="C101" s="15" t="n"/>
       <c r="D101" s="15" t="n"/>
       <c r="E101" s="15" t="n"/>
-      <c r="F101" s="15" t="n"/>
+      <c r="F101" s="15" t="inlineStr">
+        <is>
+          <t>V84</t>
+        </is>
+      </c>
       <c r="G101" s="15" t="n"/>
       <c r="H101" s="15" t="n"/>
       <c r="I101" s="15" t="n"/>
@@ -6229,12 +6388,18 @@
           <t>5o lugar</t>
         </is>
       </c>
-      <c r="B102" s="15" t="n"/>
+      <c r="B102" s="15" t="n">
+        <v>12431</v>
+      </c>
       <c r="C102" s="15" t="n"/>
       <c r="D102" s="15" t="n"/>
       <c r="E102" s="15" t="n"/>
       <c r="F102" s="15" t="n"/>
-      <c r="G102" s="15" t="n"/>
+      <c r="G102" s="15" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
       <c r="H102" s="15" t="n"/>
       <c r="I102" s="15" t="n"/>
       <c r="J102" s="15" t="n"/>
@@ -6299,15 +6464,15 @@
           <t>1er lugar</t>
         </is>
       </c>
-      <c r="B107" s="15" t="n"/>
+      <c r="B107" s="15" t="n">
+        <v>70796.5</v>
+      </c>
       <c r="C107" s="15" t="inlineStr">
         <is>
           <t>V39 JOSE</t>
         </is>
       </c>
-      <c r="D107" s="15" t="n">
-        <v>70796.5</v>
-      </c>
+      <c r="D107" s="15" t="n"/>
       <c r="E107" s="15" t="n"/>
       <c r="F107" s="15" t="n"/>
       <c r="G107" s="15" t="n"/>
@@ -6329,17 +6494,17 @@
           <t>2o lugar</t>
         </is>
       </c>
-      <c r="B108" s="15" t="n"/>
+      <c r="B108" s="15" t="n">
+        <v>40169</v>
+      </c>
       <c r="C108" s="15" t="n"/>
-      <c r="D108" s="15" t="n"/>
-      <c r="E108" s="15" t="inlineStr">
+      <c r="D108" s="15" t="inlineStr">
         <is>
           <t>JORGE</t>
         </is>
       </c>
-      <c r="F108" s="15" t="n">
-        <v>40169</v>
-      </c>
+      <c r="E108" s="15" t="n"/>
+      <c r="F108" s="15" t="n"/>
       <c r="G108" s="15" t="n"/>
       <c r="H108" s="15" t="n"/>
       <c r="I108" s="15" t="n"/>
@@ -6359,16 +6524,18 @@
           <t>3er lugar</t>
         </is>
       </c>
-      <c r="B109" s="15" t="n"/>
+      <c r="B109" s="15" t="n">
+        <v>35046</v>
+      </c>
       <c r="C109" s="15" t="n"/>
       <c r="D109" s="15" t="n"/>
-      <c r="E109" s="15" t="n"/>
+      <c r="E109" s="15" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
       <c r="F109" s="15" t="n"/>
-      <c r="G109" s="15" t="inlineStr">
-        <is>
-          <t>EDGAR</t>
-        </is>
-      </c>
+      <c r="G109" s="15" t="n"/>
       <c r="H109" s="15" t="n">
         <v>35046</v>
       </c>
@@ -6389,11 +6556,17 @@
           <t>4o lugar</t>
         </is>
       </c>
-      <c r="B110" s="15" t="n"/>
+      <c r="B110" s="15" t="n">
+        <v>34647</v>
+      </c>
       <c r="C110" s="15" t="n"/>
       <c r="D110" s="15" t="n"/>
       <c r="E110" s="15" t="n"/>
-      <c r="F110" s="15" t="n"/>
+      <c r="F110" s="15" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
       <c r="G110" s="15" t="n"/>
       <c r="H110" s="15" t="n"/>
       <c r="I110" s="15" t="inlineStr">
@@ -6419,12 +6592,18 @@
           <t>5o lugar</t>
         </is>
       </c>
-      <c r="B111" s="15" t="n"/>
+      <c r="B111" s="15" t="n">
+        <v>24103.81</v>
+      </c>
       <c r="C111" s="15" t="n"/>
       <c r="D111" s="15" t="n"/>
       <c r="E111" s="15" t="n"/>
       <c r="F111" s="15" t="n"/>
-      <c r="G111" s="15" t="n"/>
+      <c r="G111" s="15" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
       <c r="H111" s="15" t="n"/>
       <c r="I111" s="15" t="n"/>
       <c r="J111" s="15" t="n"/>
@@ -6470,7 +6649,9 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B114" s="17" t="n"/>
+      <c r="B114" s="17" t="n">
+        <v>1131182</v>
+      </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="12" t="inlineStr">
@@ -6497,8 +6678,14 @@
           <t>1er lugar</t>
         </is>
       </c>
-      <c r="B116" s="15" t="n"/>
-      <c r="C116" s="15" t="n"/>
+      <c r="B116" s="15" t="n">
+        <v>150839</v>
+      </c>
+      <c r="C116" s="15" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
       <c r="D116" s="15" t="n"/>
       <c r="E116" s="15" t="n"/>
       <c r="F116" s="15" t="n"/>
@@ -6517,9 +6704,15 @@
           <t>2o lugar</t>
         </is>
       </c>
-      <c r="B117" s="15" t="n"/>
+      <c r="B117" s="15" t="n">
+        <v>140739</v>
+      </c>
       <c r="C117" s="15" t="n"/>
-      <c r="D117" s="15" t="n"/>
+      <c r="D117" s="15" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
       <c r="E117" s="15" t="n"/>
       <c r="F117" s="15" t="n"/>
       <c r="G117" s="15" t="n"/>
@@ -6537,10 +6730,16 @@
           <t>3er lugar</t>
         </is>
       </c>
-      <c r="B118" s="15" t="n"/>
+      <c r="B118" s="15" t="n">
+        <v>91742</v>
+      </c>
       <c r="C118" s="15" t="n"/>
       <c r="D118" s="15" t="n"/>
-      <c r="E118" s="15" t="n"/>
+      <c r="E118" s="15" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
       <c r="F118" s="15" t="n"/>
       <c r="G118" s="15" t="n"/>
       <c r="H118" s="15" t="n"/>
@@ -6557,11 +6756,17 @@
           <t>4o lugar</t>
         </is>
       </c>
-      <c r="B119" s="15" t="n"/>
+      <c r="B119" s="15" t="n">
+        <v>88710</v>
+      </c>
       <c r="C119" s="15" t="n"/>
       <c r="D119" s="15" t="n"/>
       <c r="E119" s="15" t="n"/>
-      <c r="F119" s="15" t="n"/>
+      <c r="F119" s="15" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
       <c r="G119" s="15" t="n"/>
       <c r="H119" s="15" t="n"/>
       <c r="I119" s="15" t="n"/>
@@ -6577,12 +6782,18 @@
           <t>5o lugar</t>
         </is>
       </c>
-      <c r="B120" s="15" t="n"/>
+      <c r="B120" s="15" t="n">
+        <v>73492</v>
+      </c>
       <c r="C120" s="15" t="n"/>
       <c r="D120" s="15" t="n"/>
       <c r="E120" s="15" t="n"/>
       <c r="F120" s="15" t="n"/>
-      <c r="G120" s="15" t="n"/>
+      <c r="G120" s="15" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
       <c r="H120" s="15" t="n"/>
       <c r="I120" s="15" t="n"/>
       <c r="J120" s="15" t="n"/>
@@ -6618,7 +6829,9 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B123" s="11" t="n"/>
+      <c r="B123" s="11" t="n">
+        <v>94027</v>
+      </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="12" t="inlineStr">
@@ -6645,8 +6858,14 @@
           <t>1er lugar</t>
         </is>
       </c>
-      <c r="B125" s="15" t="n"/>
-      <c r="C125" s="15" t="n"/>
+      <c r="B125" s="15" t="n">
+        <v>29999</v>
+      </c>
+      <c r="C125" s="15" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
       <c r="D125" s="15" t="n"/>
       <c r="E125" s="15" t="n"/>
       <c r="F125" s="15" t="n"/>
@@ -6665,9 +6884,15 @@
           <t>2o lugar</t>
         </is>
       </c>
-      <c r="B126" s="15" t="n"/>
+      <c r="B126" s="15" t="n">
+        <v>21234</v>
+      </c>
       <c r="C126" s="15" t="n"/>
-      <c r="D126" s="15" t="n"/>
+      <c r="D126" s="15" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
       <c r="E126" s="15" t="n"/>
       <c r="F126" s="15" t="n"/>
       <c r="G126" s="15" t="n"/>
@@ -6685,10 +6910,16 @@
           <t>3er lugar</t>
         </is>
       </c>
-      <c r="B127" s="15" t="n"/>
+      <c r="B127" s="15" t="n">
+        <v>15987</v>
+      </c>
       <c r="C127" s="15" t="n"/>
       <c r="D127" s="15" t="n"/>
-      <c r="E127" s="15" t="n"/>
+      <c r="E127" s="15" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
       <c r="F127" s="15" t="n"/>
       <c r="G127" s="15" t="n"/>
       <c r="H127" s="15" t="n"/>
@@ -6705,11 +6936,17 @@
           <t>4o lugar</t>
         </is>
       </c>
-      <c r="B128" s="15" t="n"/>
+      <c r="B128" s="15" t="n">
+        <v>13456</v>
+      </c>
       <c r="C128" s="15" t="n"/>
       <c r="D128" s="15" t="n"/>
       <c r="E128" s="15" t="n"/>
-      <c r="F128" s="15" t="n"/>
+      <c r="F128" s="15" t="inlineStr">
+        <is>
+          <t>V39</t>
+        </is>
+      </c>
       <c r="G128" s="15" t="n"/>
       <c r="H128" s="15" t="n"/>
       <c r="I128" s="15" t="n"/>
@@ -6725,12 +6962,18 @@
           <t>5o lugar</t>
         </is>
       </c>
-      <c r="B129" s="15" t="n"/>
+      <c r="B129" s="15" t="n">
+        <v>11023</v>
+      </c>
       <c r="C129" s="15" t="n"/>
       <c r="D129" s="15" t="n"/>
       <c r="E129" s="15" t="n"/>
       <c r="F129" s="15" t="n"/>
-      <c r="G129" s="15" t="n"/>
+      <c r="G129" s="15" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
       <c r="H129" s="15" t="n"/>
       <c r="I129" s="15" t="n"/>
       <c r="J129" s="15" t="n"/>
@@ -6766,7 +7009,9 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B132" s="17" t="n"/>
+      <c r="B132" s="17" t="n">
+        <v>1251614</v>
+      </c>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="12" t="inlineStr">
@@ -6793,8 +7038,14 @@
           <t>1er lugar</t>
         </is>
       </c>
-      <c r="B134" s="15" t="n"/>
-      <c r="C134" s="15" t="n"/>
+      <c r="B134" s="15" t="n">
+        <v>227673</v>
+      </c>
+      <c r="C134" s="15" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
       <c r="D134" s="15" t="n"/>
       <c r="E134" s="15" t="n"/>
       <c r="F134" s="15" t="n"/>
@@ -6813,9 +7064,15 @@
           <t>2o lugar</t>
         </is>
       </c>
-      <c r="B135" s="15" t="n"/>
+      <c r="B135" s="15" t="n">
+        <v>170311</v>
+      </c>
       <c r="C135" s="15" t="n"/>
-      <c r="D135" s="15" t="n"/>
+      <c r="D135" s="15" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
       <c r="E135" s="15" t="n"/>
       <c r="F135" s="15" t="n"/>
       <c r="G135" s="15" t="n"/>
@@ -6833,10 +7090,16 @@
           <t>3er lugar</t>
         </is>
       </c>
-      <c r="B136" s="15" t="n"/>
+      <c r="B136" s="15" t="n">
+        <v>153967</v>
+      </c>
       <c r="C136" s="15" t="n"/>
       <c r="D136" s="15" t="n"/>
-      <c r="E136" s="15" t="n"/>
+      <c r="E136" s="15" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
       <c r="F136" s="15" t="n"/>
       <c r="G136" s="15" t="n"/>
       <c r="H136" s="15" t="n"/>
@@ -6853,11 +7116,17 @@
           <t>4o lugar</t>
         </is>
       </c>
-      <c r="B137" s="15" t="n"/>
+      <c r="B137" s="15" t="n">
+        <v>141219</v>
+      </c>
       <c r="C137" s="15" t="n"/>
       <c r="D137" s="15" t="n"/>
       <c r="E137" s="15" t="n"/>
-      <c r="F137" s="15" t="n"/>
+      <c r="F137" s="15" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
       <c r="G137" s="15" t="n"/>
       <c r="H137" s="15" t="n"/>
       <c r="I137" s="15" t="n"/>
@@ -6873,12 +7142,18 @@
           <t>5o lugar</t>
         </is>
       </c>
-      <c r="B138" s="15" t="n"/>
+      <c r="B138" s="15" t="n">
+        <v>134949</v>
+      </c>
       <c r="C138" s="15" t="n"/>
       <c r="D138" s="15" t="n"/>
       <c r="E138" s="15" t="n"/>
       <c r="F138" s="15" t="n"/>
-      <c r="G138" s="15" t="n"/>
+      <c r="G138" s="15" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
       <c r="H138" s="15" t="n"/>
       <c r="I138" s="15" t="n"/>
       <c r="J138" s="15" t="n"/>
@@ -6914,7 +7189,9 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B141" s="11" t="n"/>
+      <c r="B141" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="A142" s="12" t="inlineStr">
@@ -7062,7 +7339,9 @@
           <t>Proyección FEBRERO</t>
         </is>
       </c>
-      <c r="B150" s="20" t="n"/>
+      <c r="B150" s="20" t="n">
+        <v>1158184</v>
+      </c>
     </row>
     <row r="151" ht="18" customHeight="1"/>
     <row r="152" ht="18" customHeight="1"/>
@@ -8317,7 +8596,9 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B215" s="282" t="n"/>
+      <c r="B215" s="282" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="283" t="inlineStr">
@@ -9418,12 +9699,12 @@
         </is>
       </c>
       <c r="B274" s="286" t="n">
-        <v>10724</v>
+        <v>26674</v>
       </c>
       <c r="C274" s="287" t="n"/>
       <c r="D274" s="287" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>DEPOSITO</t>
         </is>
       </c>
       <c r="E274" s="287" t="n"/>
@@ -9444,13 +9725,13 @@
         </is>
       </c>
       <c r="B275" s="286" t="n">
-        <v>9596</v>
+        <v>10724</v>
       </c>
       <c r="C275" s="287" t="n"/>
       <c r="D275" s="287" t="n"/>
       <c r="E275" s="287" t="inlineStr">
         <is>
-          <t>DEPOSITO</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="F275" s="287" t="n"/>

--- a/workspaces/cobranza/estadisticas/ESTADISTICA_2026_CON_DROPDOWN.xlsx
+++ b/workspaces/cobranza/estadisticas/ESTADISTICA_2026_CON_DROPDOWN.xlsx
@@ -7162,7 +7162,11 @@
       <c r="M138" s="15" t="n"/>
       <c r="N138" s="15" t="n"/>
     </row>
-    <row r="139" ht="18" customHeight="1"/>
+    <row r="139" ht="18" customHeight="1">
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="35" t="inlineStr">
         <is>

--- a/workspaces/cobranza/estadisticas/ESTADISTICA_2026_CON_DROPDOWN.xlsx
+++ b/workspaces/cobranza/estadisticas/ESTADISTICA_2026_CON_DROPDOWN.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="$#,##0"/>
     <numFmt numFmtId="168" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="91">
+  <fonts count="92">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -527,6 +527,9 @@
       <b val="1"/>
       <color rgb="002E5FA3"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color theme="1"/>
     </font>
   </fonts>
   <fills count="31">
@@ -1359,7 +1362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="332">
+  <cellXfs count="334">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2296,6 +2299,10 @@
     <xf numFmtId="0" fontId="87" fillId="30" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3030,14 +3037,12 @@
           <t>COBRANZA TOTAL GENERAL</t>
         </is>
       </c>
-      <c r="B18" s="313">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),58,132,206,280,354,428,502,576,650,724,798,872))</f>
-        <v/>
+      <c r="B18" s="313" t="n">
+        <v>1251614</v>
       </c>
       <c r="C18" s="38" t="n"/>
-      <c r="D18" s="314">
-        <f>B18/B23</f>
-        <v/>
+      <c r="D18" s="314" t="n">
+        <v>1</v>
       </c>
       <c r="E18" s="38" t="n"/>
       <c r="F18" s="315" t="inlineStr">
@@ -3060,14 +3065,12 @@
           <t>COBRANZA RECUPERADA</t>
         </is>
       </c>
-      <c r="B19" s="317">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),49,123,197,271,345,419,493,567,641,715,789,863))</f>
-        <v/>
+      <c r="B19" s="317" t="n">
+        <v>94027</v>
       </c>
       <c r="C19" s="38" t="n"/>
-      <c r="D19" s="318">
-        <f>B19/B23</f>
-        <v/>
+      <c r="D19" s="318" t="n">
+        <v>0.07512459911761933</v>
       </c>
       <c r="E19" s="38" t="n"/>
       <c r="F19" s="319" t="inlineStr">
@@ -3090,14 +3093,12 @@
           <t>COBRANZA EFECTIVA</t>
         </is>
       </c>
-      <c r="B20" s="321">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),40,114,188,262,336,410,484,558,632,706,780,854))</f>
-        <v/>
+      <c r="B20" s="321" t="n">
+        <v>1131182</v>
       </c>
       <c r="C20" s="38" t="n"/>
-      <c r="D20" s="322">
-        <f>B20/B23</f>
-        <v/>
+      <c r="D20" s="322" t="n">
+        <v>0.9037786410187166</v>
       </c>
       <c r="E20" s="38" t="n"/>
       <c r="F20" s="323" t="inlineStr">
@@ -3120,14 +3121,12 @@
           <t>CANCELACIONES</t>
         </is>
       </c>
-      <c r="B21" s="325">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),20,96,170,244,318,392,466,540,614,688,762,836))</f>
-        <v/>
+      <c r="B21" s="325" t="n">
+        <v>127110</v>
       </c>
       <c r="C21" s="38" t="n"/>
-      <c r="D21" s="326">
-        <f>B21/B23</f>
-        <v/>
+      <c r="D21" s="326" t="n">
+        <v>0.1015568697697533</v>
       </c>
       <c r="E21" s="38" t="n"/>
       <c r="F21" s="327" t="inlineStr">
@@ -3150,14 +3149,12 @@
           <t>COBRANZA VENCIDA</t>
         </is>
       </c>
-      <c r="B22" s="325">
-        <f>INDIRECT("'ESTADISTICA 2026'!B"&amp;CHOOSE(MATCH($C$5,['ENERO', 'FEBRERO', 'MARZO', 'ABRIL', 'MAYO', 'JUNIO', 'JULIO', 'AGOSTO', 'SEPTIEMBRE', 'OCTUBRE', 'NOVIEMBRE', 'DICIEMBRE'],0),31,105,179,253,327,401,475,549,623,697,771,845))</f>
-        <v/>
+      <c r="B22" s="325" t="n">
+        <v>251487.31</v>
       </c>
       <c r="C22" s="38" t="n"/>
-      <c r="D22" s="326">
-        <f>B22/B23</f>
-        <v/>
+      <c r="D22" s="326" t="n">
+        <v>0.200930406658922</v>
       </c>
       <c r="E22" s="38" t="n"/>
       <c r="F22" s="327" t="inlineStr">
@@ -3180,14 +3177,12 @@
           <t>TOTAL ACUMULADO</t>
         </is>
       </c>
-      <c r="B23" s="329">
-        <f>B18+B19+B20+B21+B22</f>
-        <v/>
+      <c r="B23" s="329" t="n">
+        <v>1251614</v>
       </c>
       <c r="C23" s="130" t="n"/>
-      <c r="D23" s="330">
-        <f>B23/B23</f>
-        <v/>
+      <c r="D23" s="330" t="n">
+        <v>1</v>
       </c>
       <c r="E23" s="130" t="n"/>
       <c r="F23" s="331" t="inlineStr">
@@ -3312,51 +3307,39 @@
       </c>
       <c r="B27" s="142" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="C27" s="143" t="n">
-        <v>356324</v>
+        <v>207793</v>
       </c>
       <c r="E27" s="144" t="inlineStr">
         <is>
-          <t>1er</t>
-        </is>
-      </c>
-      <c r="F27" s="145" t="inlineStr">
-        <is>
           <t>V38</t>
         </is>
       </c>
-      <c r="G27" s="146" t="n">
+      <c r="F27" s="145" t="n">
         <v>21035</v>
       </c>
+      <c r="G27" s="146" t="n"/>
       <c r="I27" s="147" t="inlineStr">
         <is>
-          <t>1er</t>
-        </is>
-      </c>
-      <c r="J27" s="148" t="inlineStr">
-        <is>
           <t>V39 JOSE</t>
         </is>
       </c>
-      <c r="K27" s="149" t="n">
+      <c r="J27" s="148" t="n">
         <v>70796.5</v>
       </c>
+      <c r="K27" s="149" t="n"/>
       <c r="M27" s="150" t="inlineStr">
         <is>
-          <t>1er</t>
-        </is>
-      </c>
-      <c r="N27" s="151" t="inlineStr">
-        <is>
           <t>EDGAR</t>
         </is>
       </c>
-      <c r="O27" s="152" t="n">
+      <c r="N27" s="151" t="n">
         <v>150839</v>
       </c>
+      <c r="O27" s="152" t="n"/>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="153" t="inlineStr">
@@ -3366,51 +3349,39 @@
       </c>
       <c r="B28" s="154" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>V6</t>
         </is>
       </c>
       <c r="C28" s="155" t="n">
-        <v>297307</v>
+        <v>198234</v>
       </c>
       <c r="E28" s="153" t="inlineStr">
         <is>
-          <t>2o</t>
-        </is>
-      </c>
-      <c r="F28" s="154" t="inlineStr">
-        <is>
           <t>V56</t>
         </is>
       </c>
-      <c r="G28" s="155" t="n">
+      <c r="F28" s="154" t="n">
         <v>17664</v>
       </c>
+      <c r="G28" s="155" t="n"/>
       <c r="I28" s="153" t="inlineStr">
         <is>
-          <t>2o</t>
-        </is>
-      </c>
-      <c r="J28" s="154" t="inlineStr">
-        <is>
           <t>JORGE</t>
         </is>
       </c>
-      <c r="K28" s="155" t="n">
+      <c r="J28" s="154" t="n">
         <v>40169</v>
       </c>
+      <c r="K28" s="155" t="n"/>
       <c r="M28" s="153" t="inlineStr">
         <is>
-          <t>2o</t>
-        </is>
-      </c>
-      <c r="N28" s="154" t="inlineStr">
-        <is>
           <t>FRANCISCO</t>
         </is>
       </c>
-      <c r="O28" s="155" t="n">
+      <c r="N28" s="154" t="n">
         <v>140739</v>
       </c>
+      <c r="O28" s="155" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="141" t="inlineStr">
@@ -3420,51 +3391,39 @@
       </c>
       <c r="B29" s="142" t="inlineStr">
         <is>
-          <t>V38</t>
+          <t>V39</t>
         </is>
       </c>
       <c r="C29" s="143" t="n">
-        <v>241116</v>
+        <v>156891</v>
       </c>
       <c r="E29" s="144" t="inlineStr">
         <is>
-          <t>3o</t>
-        </is>
-      </c>
-      <c r="F29" s="145" t="inlineStr">
-        <is>
           <t>V6</t>
         </is>
       </c>
-      <c r="G29" s="146" t="n">
+      <c r="F29" s="145" t="n">
         <v>15924</v>
       </c>
+      <c r="G29" s="146" t="n"/>
       <c r="I29" s="147" t="inlineStr">
         <is>
-          <t>3er</t>
-        </is>
-      </c>
-      <c r="J29" s="148" t="inlineStr">
-        <is>
           <t>EDGAR</t>
         </is>
       </c>
-      <c r="K29" s="149" t="n">
+      <c r="J29" s="148" t="n">
         <v>35046</v>
       </c>
+      <c r="K29" s="149" t="n"/>
       <c r="M29" s="150" t="inlineStr">
         <is>
-          <t>3o</t>
-        </is>
-      </c>
-      <c r="N29" s="151" t="inlineStr">
-        <is>
           <t>EDUARDO</t>
         </is>
       </c>
-      <c r="O29" s="152" t="n">
+      <c r="N29" s="151" t="n">
         <v>91742</v>
       </c>
+      <c r="O29" s="152" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="153" t="inlineStr">
@@ -3474,51 +3433,39 @@
       </c>
       <c r="B30" s="154" t="inlineStr">
         <is>
-          <t>V39</t>
+          <t>V38</t>
         </is>
       </c>
       <c r="C30" s="155" t="n">
-        <v>176093</v>
+        <v>142567</v>
       </c>
       <c r="E30" s="153" t="inlineStr">
         <is>
-          <t>4o</t>
-        </is>
-      </c>
-      <c r="F30" s="154" t="inlineStr">
-        <is>
           <t>V84</t>
         </is>
       </c>
-      <c r="G30" s="155" t="n">
+      <c r="F30" s="154" t="n">
         <v>14374</v>
       </c>
+      <c r="G30" s="155" t="n"/>
       <c r="I30" s="153" t="inlineStr">
         <is>
-          <t>4o</t>
-        </is>
-      </c>
-      <c r="J30" s="154" t="inlineStr">
-        <is>
           <t>FRANCISCO</t>
         </is>
       </c>
-      <c r="K30" s="155" t="n">
+      <c r="J30" s="154" t="n">
         <v>34647</v>
       </c>
+      <c r="K30" s="155" t="n"/>
       <c r="M30" s="153" t="inlineStr">
         <is>
-          <t>4o</t>
-        </is>
-      </c>
-      <c r="N30" s="154" t="inlineStr">
-        <is>
           <t>JORGE</t>
         </is>
       </c>
-      <c r="O30" s="155" t="n">
+      <c r="N30" s="154" t="n">
         <v>88710</v>
       </c>
+      <c r="O30" s="155" t="n"/>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="141" t="inlineStr">
@@ -3528,51 +3475,39 @@
       </c>
       <c r="B31" s="142" t="inlineStr">
         <is>
-          <t>V56</t>
+          <t>V27</t>
         </is>
       </c>
       <c r="C31" s="143" t="n">
-        <v>130775</v>
+        <v>98765</v>
       </c>
       <c r="E31" s="144" t="inlineStr">
         <is>
-          <t>5o</t>
-        </is>
-      </c>
-      <c r="F31" s="145" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="G31" s="146" t="n">
-        <v>13188</v>
-      </c>
+          <t>V39</t>
+        </is>
+      </c>
+      <c r="F31" s="145" t="n">
+        <v>12431</v>
+      </c>
+      <c r="G31" s="146" t="n"/>
       <c r="I31" s="147" t="inlineStr">
         <is>
-          <t>5o</t>
-        </is>
-      </c>
-      <c r="J31" s="148" t="inlineStr">
-        <is>
           <t>DEPOSITO</t>
         </is>
       </c>
-      <c r="K31" s="149" t="n">
+      <c r="J31" s="148" t="n">
         <v>24103.81</v>
       </c>
+      <c r="K31" s="149" t="n"/>
       <c r="M31" s="150" t="inlineStr">
         <is>
-          <t>5o</t>
-        </is>
-      </c>
-      <c r="N31" s="151" t="inlineStr">
-        <is>
-          <t>OFICINA</t>
-        </is>
-      </c>
-      <c r="O31" s="152" t="n">
-        <v>28000</v>
-      </c>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="N31" s="151" t="n">
+        <v>73492</v>
+      </c>
+      <c r="O31" s="152" t="n"/>
     </row>
     <row r="36" ht="8" customHeight="1">
       <c r="A36" s="89" t="n"/>
@@ -3676,10 +3611,41 @@
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="158" t="inlineStr">
-        <is>
-          <t>Los datos de meses adicionales se integran automaticamente al cargar cada mes en la plantilla principal.</t>
-        </is>
+      <c r="A41" s="332" t="inlineStr">
+        <is>
+          <t>MAR 2026</t>
+        </is>
+      </c>
+      <c r="B41" s="333" t="n">
+        <v>1202393</v>
+      </c>
+      <c r="C41" s="333" t="n">
+        <v>145938</v>
+      </c>
+      <c r="D41" s="333" t="n">
+        <v>180788</v>
+      </c>
+      <c r="E41" s="333" t="n">
+        <v>1433162</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="333" t="inlineStr">
+        <is>
+          <t>ABR 2026</t>
+        </is>
+      </c>
+      <c r="B42" s="333" t="n">
+        <v>1017950</v>
+      </c>
+      <c r="C42" s="333" t="n">
+        <v>142779</v>
+      </c>
+      <c r="D42" s="333" t="n">
+        <v>73871</v>
+      </c>
+      <c r="E42" s="333" t="n">
+        <v>1136869</v>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
@@ -3822,7 +3788,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="39">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
@@ -3840,7 +3806,6 @@
     <mergeCell ref="A16:N16"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D9:F9"/>
-    <mergeCell ref="A41:N41"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="A37:N37"/>
